--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -159,6 +159,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -775,73 +778,73 @@
         <v>186.2</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>28.8</v>
+        <v>28.2</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="H4" s="8" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.9</v>
+        <v>2.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>20.2</v>
+        <v>2.2</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>20.1</v>
+        <v>26.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>28.7</v>
+        <v>28.2</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.8</v>
+        <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>168.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>811.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -857,7 +860,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>403.5</v>
+        <v>438.5</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>32.6</v>
@@ -872,16 +875,16 @@
         <v>14.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>16.8</v>
+        <v>6.2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>32.5</v>
+        <v>3.5</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>18.9</v>
@@ -890,10 +893,10 @@
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>28.6</v>
+        <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.2</v>
@@ -908,22 +911,22 @@
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>156.6</v>
+        <v>56.6</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>27.2</v>
+        <v>87.2</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X5" s="8" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>8.199999999999999</v>
@@ -942,28 +945,28 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>422.3</v>
+        <v>22.3</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>34.2</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G6" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>11.6</v>
+        <v>4.6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -971,14 +974,14 @@
       <c r="L6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>20</v>
+      <c r="M6" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0</v>
@@ -993,13 +996,13 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>55.2</v>
+        <v>51.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.7</v>
+        <v>28.2</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>23.7</v>
@@ -1011,7 +1014,7 @@
         <v>66.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>4.1</v>
+        <v>13.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1027,16 +1030,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4335.1</v>
+        <v>4778.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>34.7</v>
+        <v>24.7</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>15.4</v>
@@ -1045,10 +1048,10 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>43.3</v>
+        <v>2.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1057,16 +1060,16 @@
         <v>20.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.1</v>
+        <v>2.1</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>35.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>34.2</v>
@@ -1075,7 +1078,7 @@
         <v>25.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>50.6</v>
@@ -1087,16 +1090,16 @@
         <v>29.5</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>24.4</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>27.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>13.8</v>
+        <v>438.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1112,28 +1115,28 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>299</v>
+        <v>299.6</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>34.41</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="G8" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G8" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>119</v>
+      <c r="H8" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>30.9</v>
@@ -1151,28 +1154,28 @@
         <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>10.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>21.9</v>
+        <v>24.9</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>26.1</v>
@@ -1181,7 +1184,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.6</v>
+        <v>26.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1203,7 +1206,7 @@
         <v>164.8</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>130.8</v>
@@ -1221,22 +1224,22 @@
         <v>27.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>30.9</v>
+        <v>3.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>100.2</v>
+        <v>16.2</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>115.8</v>
+        <v>15.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1894.5</v>
+        <v>494.5</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>149.6</v>
@@ -1248,7 +1251,7 @@
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>229.9</v>
+        <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>81</v>
@@ -1265,7 +1268,13 @@
       <c r="Y9" s="3" t="n">
         <v>388.8</v>
       </c>
-      <c r="Z9" s="3" t="n"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222424272
+777
+</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1295,7 +1304,7 @@
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>17.9</v>
+        <v>12.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
@@ -1303,48 +1312,54 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n">
-        <v>20</v>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+2221
+</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.1</v>
+        <v>2.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>66</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>16.2</v>
+        <v>1.2</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="W10" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>77.8</v>
+        <v>272.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>41.6</v>
@@ -1366,7 +1381,7 @@
         <v>265.6</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>19.8</v>
@@ -1374,17 +1389,17 @@
       <c r="F11" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>10.3</v>
+      <c r="G11" s="3" t="n">
+        <v>1.3</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="I11" s="8" t="n">
-        <v>86.59999999999999</v>
+      <c r="I11" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>82.8</v>
+        <v>2.8</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1395,11 +1410,16 @@
       <c r="M11" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>92.3</v>
+      <c r="N11" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+505
+1799
+</t>
+        </is>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
@@ -1407,32 +1427,36 @@
       <c r="Q11" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R11" s="8" t="n">
+      <c r="R11" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="S11" s="8" t="n">
+      <c r="S11" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="U11" s="8" t="n">
+        <v>720.6</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" s="8" t="n">
+      <c r="V11" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W11" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>24</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+744
+</t>
+        </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1448,7 +1472,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>347.1</v>
+        <v>342.4</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>31.8</v>
@@ -1468,11 +1492,11 @@
       <c r="I12" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <v>44.6</v>
+      <c r="J12" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>23.3</v>
@@ -1481,10 +1505,10 @@
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>27.9</v>
+        <v>2.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>97.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
@@ -1502,22 +1526,22 @@
         <v>57.8</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W12" s="8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W12" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>76.7</v>
+        <v>7.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>5.7</v>
+        <v>57.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1533,7 +1557,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1428.6</v>
+        <v>428.6</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>32.8</v>
@@ -1554,13 +1578,13 @@
         <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="8" t="n">
-        <v>22.1</v>
+      <c r="L13" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>21.9</v>
@@ -1569,10 +1593,10 @@
         <v>26.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>98</v>
+        <v>9.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.4</v>
+        <v>26.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
@@ -1589,8 +1613,8 @@
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="8" t="n">
-        <v>28</v>
+      <c r="V13" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>24.8</v>
@@ -1599,10 +1623,10 @@
         <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>23.1</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1633,34 +1657,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>20.3</v>
+        <v>2.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>52.1</v>
+        <v>22.1</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>22.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>97.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>21.1</v>
@@ -1675,10 +1699,10 @@
         <v>2.9</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>21.6</v>
+        <v>26</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>41.6</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>25.5</v>
@@ -1687,7 +1711,7 @@
         <v>96</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1703,7 +1727,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>359.6</v>
+        <v>5.6</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>32.5</v>
@@ -1714,11 +1738,11 @@
       <c r="F15" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>419.6</v>
+      <c r="G15" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>2.4</v>
@@ -1727,7 +1751,7 @@
         <v>3.9</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
@@ -1739,7 +1763,7 @@
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>180</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
@@ -1751,7 +1775,7 @@
         <v>25.8</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>89.2</v>
+        <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>61.7</v>
@@ -1763,7 +1787,7 @@
         <v>28.7</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>24.8</v>
+        <v>4.8</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>28.8</v>
@@ -1772,7 +1796,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.9</v>
+        <v>20.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1793,17 +1817,17 @@
       <c r="D16" s="10" t="n">
         <v>157.9</v>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>131.7</v>
-      </c>
-      <c r="G16" s="10" t="n">
+      <c r="E16" s="14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>1317.2</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>99.2</v>
+        <v>929.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.5</v>
@@ -1811,19 +1835,37 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">790691
+22
+5682
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>10.6</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>130.7</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>490.1</v>
+        <v>19.5</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">791727
+14
+000
+</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11722
+77218
+</t>
+        </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>148.7</v>
@@ -1835,24 +1877,42 @@
         <v>136.1</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>331.8</v>
+        <v>31.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="3" t="n">
-        <v>133.7</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>120.7</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>142.5</v>
-      </c>
-      <c r="Y16" s="3" t="n">
-        <v>407.4</v>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7277978
+7566
+</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22414
+8711011466 7
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36595
+99781
+</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5555
+5721
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>741.1</v>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1867,22 +1927,22 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>318.2</v>
+        <v>38.2</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>10.5</v>
       </c>
-      <c r="H17" s="3" t="n">
-        <v>19.8</v>
+      <c r="H17" s="8" t="n">
+        <v>292.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>2.3</v>
@@ -1893,20 +1953,20 @@
       <c r="K17" s="3" t="n">
         <v>36.8</v>
       </c>
-      <c r="L17" s="8" t="n">
-        <v>10.6</v>
+      <c r="L17" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>26.1</v>
+      <c r="N17" s="8" t="n">
+        <v>30.7</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>10.4</v>
+        <v>490.1</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>29.7</v>
@@ -1914,26 +1974,26 @@
       <c r="R17" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S17" s="8" t="n">
-        <v>72.2</v>
+      <c r="S17" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="8" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="W17" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="W17" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>28.5</v>
+      <c r="X17" s="8" t="n">
+        <v>42.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>81.5</v>
+        <v>47.6</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>6.9</v>
@@ -1955,16 +2015,16 @@
         <v>368</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>10.9</v>
+        <v>26.6</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>20.4</v>
@@ -1973,20 +2033,30 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K18" s="3" t="n"/>
+        <v>4.3</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+222
+</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="n">
-        <v>22.1</v>
+        <v>24.4</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>92.3</v>
+        <v>26.1</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27844
+171719
+</t>
+        </is>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -1994,32 +2064,40 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>27.7</v>
+        <v>7.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U18" s="8" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>28.5</v>
+        <v>26.7</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Y18" s="3" t="n">
-        <v>71.7</v>
+        <v>4.1</v>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7444
+1779 7
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09442
+77 7
+</t>
+        </is>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>1.1</v>
+        <v>17.1</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2038,15 +2116,15 @@
         <v>265.6</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>22.2</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="G19" s="10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2059,19 +2137,19 @@
         <v>2.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>10.4</v>
+        <v>1.4</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>21.4</v>
+        <v>2.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>26.3</v>
+        <v>24.8</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>297.3</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.6</v>
@@ -2091,17 +2169,17 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="8" t="n">
-        <v>24.3</v>
+      <c r="V19" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>22.9</v>
+        <v>24.4</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>21.4</v>
+        <v>2.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>22</v>
+        <v>7218.7</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.3</v>
@@ -2126,7 +2204,7 @@
         <v>31.4</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>26.5</v>
@@ -2141,26 +2219,24 @@
         <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>25.4</v>
+        <v>26.3</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="P20" s="3" t="n"/>
       <c r="Q20" s="3" t="n">
         <v>30.7</v>
       </c>
@@ -2174,19 +2250,19 @@
         <v>62.3</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>16.6</v>
+        <v>1.6</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>27.3</v>
+        <v>24.3</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>23.8</v>
+        <v>2.9</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>9.1</v>
@@ -2208,7 +2284,7 @@
         <v>340.8</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>21.2</v>
@@ -2229,22 +2305,22 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>21.6</v>
+        <v>2.6</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>986</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.6</v>
@@ -2256,22 +2332,22 @@
         <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>71.2</v>
+        <v>4.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>12.6</v>
+        <v>1.6</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>27.8</v>
+        <v>2.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>24.6</v>
+        <v>23.8</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>28.9</v>
+        <v>7.2</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>772.3</v>
+        <v>75</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2290,22 +2366,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>399.3</v>
-      </c>
-      <c r="D22" s="10" t="n">
+        <v>395.3</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="G22" s="10" t="n">
-        <v>11.8</v>
+      <c r="F22" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.5</v>
@@ -2314,22 +2390,25 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>21.6</v>
+        <v>0.6</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>24.7</v>
+        <v>25.6</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0.4</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68 2
+</t>
+        </is>
       </c>
       <c r="Q22" s="3" t="n">
         <v>32.4</v>
@@ -2340,23 +2419,26 @@
       <c r="S22" s="3" t="n">
         <v>89.3</v>
       </c>
-      <c r="T22" s="3" t="n">
-        <v>60.5</v>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65 2
+</t>
+        </is>
       </c>
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>26.5</v>
+        <v>27.8</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>29.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>86</v>
+        <v>72.3</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>4.9</v>
@@ -2375,43 +2457,62 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1739.6</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>2.2</v>
+        <v>739.6</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>57.8</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>132.4</v>
+        <v>32.5</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>50.3</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>19.3</v>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41444444
+1
+8684
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27955
+42
+12141
+</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+1141089
+</t>
+        </is>
       </c>
       <c r="K23" s="3" t="n">
         <v>7.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.7</v>
+        <v>18.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>1489.4</v>
+        <v>24.7</v>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418686866
+50756012
+1441
+</t>
+        </is>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
@@ -2423,28 +2524,28 @@
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1146.8</v>
+        <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>395.7</v>
+        <v>325.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>792.4</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>134.4</v>
+        <v>86.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>120.3</v>
+        <v>24.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>1408.1</v>
+        <v>2.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>3940.4</v>
+        <v>860.6</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2460,73 +2561,81 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.9</v>
+        <v>739.6</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>21.4</v>
+        <v>57.8</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>7.2</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <v>10.1</v>
+        <v>32.5</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>50.3</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>3.9</v>
+        <v>19.3</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="L24" s="8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N24" s="8" t="n">
-        <v>26.8</v>
+      <c r="L24" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6169690911
+2929
+</t>
+        </is>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>29.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="R24" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>46.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>325.7</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>26.9</v>
+        <v>79.40000000000001</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>34.4</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>22.2</v>
+        <v>2.3</v>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74950
+448468
+</t>
+        </is>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>79.8</v>
+        <v>399</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>7.3</v>
@@ -2545,31 +2654,31 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>106.7</v>
+        <v>34.9</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>26.3</v>
+        <v>31.6</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>5.7</v>
+        <v>26.4</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.2</v>
+        <v>19.3</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>21.6</v>
@@ -2577,41 +2686,41 @@
       <c r="M25" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N25" s="3" t="n">
-        <v>25.4</v>
+      <c r="N25" s="8" t="n">
+        <v>26.8</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>146.1</v>
+        <v>31.1</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>156.1</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>28.7</v>
+        <v>29.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>5.3</v>
+        <v>15.9</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>244.1</v>
+        <v>26.9</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>26.8</v>
+      <c r="X25" s="8" t="n">
+        <v>40.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>79.8</v>
+        <v>2.8</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>7.3</v>
@@ -2630,76 +2739,92 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>90</v>
+        <v>16.7</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>14.1</v>
+        <v>23.5</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>5.7</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="I26" s="3" t="n">
-        <v>0.5</v>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215852
+147
+</t>
+        </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>0.2</v>
+        <v>6.8</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+77
+</t>
+        </is>
       </c>
       <c r="L26" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>924</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>1297</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>22.8</v>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7771717
+11811408 7
+</t>
+        </is>
       </c>
       <c r="X26" s="3" t="n">
-        <v>27.1</v>
+        <v>2.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>87.7</v>
       </c>
-      <c r="Z26" s="3" t="n">
-        <v>3.8</v>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+893
+</t>
+        </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2715,76 +2840,68 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>322</v>
+        <v>90</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>30.5</v>
+        <v>25.2</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>25.5</v>
+        <v>23.1</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>9.9</v>
+        <v>4.1</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="I27" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n">
-        <v>24.4</v>
+        <v>21.4</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="O27" s="3" t="n"/>
       <c r="P27" s="3" t="n">
-        <v>10.4</v>
+        <v>8</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>28.8</v>
+        <v>4.3</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>89</v>
+        <v>23.3</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>86</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>73.2</v>
+        <v>926</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>29</v>
+        <v>26.8</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2800,76 +2917,80 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2990.7</v>
+        <v>322</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>31.8</v>
+        <v>30.4</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>26.1</v>
+        <v>25.5</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>19.1</v>
+        <v>9.9</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>20.9</v>
+        <v>2</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>20.6</v>
+        <v>26.5</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="O28" s="3" t="n">
-        <v>4.9</v>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+2923
+</t>
+        </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>16.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>31.2</v>
+        <v>28.8</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>27.2</v>
+        <v>29</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>60.2</v>
+        <v>73.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.1</v>
+        <v>1.5</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>28.6</v>
+        <v>26.9</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>24.4</v>
+        <v>2.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>28.4</v>
+        <v>27.1</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2885,34 +3006,34 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3468.1</v>
+        <v>290.7</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="H29" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H29" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>28.1</v>
+        <v>21.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>20.6</v>
@@ -2920,41 +3041,45 @@
       <c r="N29" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="O29" s="3" t="n">
-        <v>195.3</v>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+2923
+</t>
+        </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q29" s="8" t="n">
-        <v>25.3</v>
+        <v>0.5</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>31.2</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>23.6</v>
+        <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>27</v>
+        <v>60.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>14.2</v>
+        <v>18.1</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>22.4</v>
+        <v>28.6</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>36.1</v>
+        <v>29.1</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>724.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2970,76 +3095,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1056.2</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>42</v>
+        <v>846.2</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>119.2</v>
+        <v>12.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111</v>
+        <v>2.6</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>38.8</v>
+        <v>8.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>106.5</v>
+        <v>21.1</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1159.2</v>
+        <v>20.6</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>487.6</v>
+        <v>95.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1185.8</v>
+        <v>825.3</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>120.7</v>
+        <v>23.6</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>140.9</v>
+        <v>28</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>396.8</v>
+        <v>8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>14.2</v>
+        <v>4.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>126.1</v>
+        <v>2.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>21.3</v>
+        <v>24.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>135.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>90.8</v>
+        <v>4.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3055,76 +3180,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>211.2</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G31" s="10" t="n">
-        <v>8.4</v>
+        <v>15.2</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>452.1</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>42</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>38.8</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>21.3</v>
+        <v>16.5</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>21</v>
+        <v>15.1</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.5</v>
+        <v>487.6</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>28.2</v>
+        <v>2.8</v>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>280.7</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>40.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>15.9</v>
+        <v>396.8</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>27.2</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>4.2</v>
+        <v>44.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3140,76 +3265,74 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>384.7</v>
+        <v>211.2</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>31.1</v>
+        <v>29</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>11.8</v>
+        <v>8.4</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J32" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>20.1</v>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n">
+        <v>41.3</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N32" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N32" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>100</v>
+        <v>9.5</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R32" s="8" t="n">
-        <v>24.9</v>
+        <v>7.2</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>22.5</v>
+        <v>28.2</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>61</v>
+        <v>22.9</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>17.5</v>
+        <v>8.1</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>23.2</v>
+        <v>25.2</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>15.9</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>27.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>24.9</v>
+        <v>4.9</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3225,76 +3348,74 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>213.3</v>
+        <v>384.7</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>29.2</v>
+        <v>31.1</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>24.4</v>
+        <v>25.2</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>51.6</v>
+        <v>4.4</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>23.5</v>
+        <v>20</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>23.3</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>84.59999999999999</v>
+        <v>31.1</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>982.1</v>
+        <v>2.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>25.6</v>
+        <v>2.4</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="Y33" s="3" t="n">
-        <v>74.59999999999999</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="Y33" s="3" t="n"/>
       <c r="Z33" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3310,76 +3431,72 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>311.6</v>
+        <v>213.3</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>31.9</v>
+        <v>29.2</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>21.5</v>
+        <v>19.6</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>26.7</v>
+        <v>24.4</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="N34" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N34" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>1199</v>
+        <v>992.6</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>20.5</v>
+        <v>28.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>25.8</v>
+        <v>4.6</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>30.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>2720.9</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>13.3</v>
+        <v>11.5</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="W34" s="8" t="n">
-        <v>138248.4</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="Y34" s="3" t="n">
-        <v>262.1</v>
-      </c>
+        <v>25.6</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="X34" s="3" t="n"/>
+      <c r="Y34" s="3" t="n"/>
       <c r="Z34" s="3" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3395,76 +3512,88 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>353.4</v>
+        <v>311.6</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>31</v>
+        <v>31.9</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>20.7</v>
+        <v>21.5</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>10.3</v>
+        <v>26.6</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>12.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+9217
+</t>
+        </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>97.8</v>
+        <v>996</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>31.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>30.5</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>26.9</v>
+        <v>25.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.5</v>
+        <v>30.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>61.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="W35" s="8" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>82</v>
+        <v>13.3</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242461
+289
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26282
+79794
+</t>
+        </is>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3480,74 +3609,74 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>430.7</v>
+        <v>353.4</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>32.1</v>
+        <v>31</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>26.5</v>
+        <v>25.9</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>19.8</v>
-      </c>
+        <v>10.3</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n">
-        <v>2.4</v>
+        <v>22.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>14.4</v>
+        <v>4</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>41</v>
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>20.7</v>
+        <v>21.3</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>972.5</v>
+        <v>97.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>10.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>32.1</v>
+        <v>31.1</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>26</v>
+        <v>24.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>29.7</v>
+        <v>27.5</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>62.2</v>
+        <v>6.3</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="W36" s="8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
+        <v>27.8</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242461
+289
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="n"/>
       <c r="Z36" s="3" t="n">
         <v>8.4</v>
       </c>
@@ -3565,76 +3694,70 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1693.7</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>155.4</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>102</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>128.7</v>
-      </c>
-      <c r="G37" s="10" t="n">
-        <v>53.4</v>
-      </c>
+        <v>430.7</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
       <c r="H37" s="3" t="n">
-        <v>96.5</v>
+        <v>13.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>10.1</v>
+        <v>2.4</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>35.6</v>
+        <v>30.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1015.9</v>
+        <v>20.7</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>24.2</v>
+        <v>242.8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1192.7</v>
+        <v>9.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>153.7</v>
+        <v>32.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>126.2</v>
+        <v>26</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1143.1</v>
+        <v>29.7</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>324.8</v>
+        <v>62.2</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>77.7</v>
+        <v>18.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>136.8</v>
+        <v>28.7</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y37" s="3" t="n">
-        <v>72</v>
-      </c>
+        <v>26.6</v>
+      </c>
+      <c r="X37" s="3" t="n"/>
+      <c r="Y37" s="3" t="n"/>
       <c r="Z37" s="3" t="n">
-        <v>1.1</v>
+        <v>7909.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3650,77 +3773,83 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>338.7</v>
+        <v>693.7</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>31</v>
+        <v>55.4</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>20.4</v>
+        <v>2</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>25.7</v>
+        <v>28.7</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>10.6</v>
+        <v>53.4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.3</v>
+        <v>96.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>18.1</v>
+        <v>4</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887 1
+18 74
+</t>
+        </is>
       </c>
       <c r="K38" s="3" t="n">
         <v>35.6</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>98.5</v>
+        <v>16</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42477
+114111
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24268701
+6888
+</t>
+        </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q38" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>28.6</v>
+        <v>1.7</v>
+      </c>
+      <c r="Q38" s="8" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="R38" s="8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>43.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>65</v>
+        <v>324.8</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>77.7</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="X38" s="3" t="n"/>
+      <c r="Y38" s="3" t="n"/>
+      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3735,76 +3864,78 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G39" s="10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.7</v>
+        <v>20.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0.6</v>
-      </c>
+        <v>18.1</v>
+      </c>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>14.8</v>
+        <v>24.1</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>492.7</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>36.7</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>86</v>
+        <v>25.2</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>89.8</v>
+        <v>28.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>63.2</v>
+        <v>65</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>32.4</v>
+      </c>
+      <c r="W39" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+1
+</t>
+        </is>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>38.6</v>
+        <v>2.9</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3820,76 +3951,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>453.7</v>
+        <v>32.5</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>32.9</v>
+        <v>31.9</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>18.8</v>
+        <v>20.3</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>18.2</v>
+        <v>11.7</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12.7</v>
+        <v>21.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>46.8</v>
+        <v>20.9</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>32.8</v>
+        <v>31.9</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="S40" s="8" t="n">
-        <v>29.3</v>
+      <c r="S40" s="3" t="n">
+        <v>89.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>20.2</v>
+        <v>63.2</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>27.3</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>27.8</v>
+        <v>24.7</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>23.8</v>
+        <v>24.3</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>26.9</v>
+        <v>2.5</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>98.2</v>
+        <v>88.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>0.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3905,76 +4036,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>265.6</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E41" s="10" t="n">
+        <v>453.7</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M41" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G41" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>28.6</v>
+      <c r="N41" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99</v>
+        <v>97.8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>21.4</v>
+        <v>32.8</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>24.9</v>
+        <v>29.3</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>92.3</v>
+        <v>59.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>28.1</v>
+        <v>2.2</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>22</v>
-      </c>
+        <v>26.9</v>
+      </c>
+      <c r="Y41" s="3" t="n"/>
       <c r="Z41" s="3" t="n">
-        <v>8.9</v>
+        <v>1</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3990,76 +4119,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>236.3</v>
+        <v>26.5</v>
       </c>
       <c r="D42" s="10" t="n">
         <v>31.6</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>20.3</v>
+        <v>19.6</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>28.7</v>
+        <v>4.6</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>21.8</v>
+        <v>19.9</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>0.2</v>
+        <v>99</v>
+      </c>
+      <c r="P42" s="8" t="n">
+        <v>12.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>24.1</v>
+        <v>22.3</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>23.8</v>
+        <v>21.4</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>89.3</v>
+        <v>24.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>97.7</v>
+        <v>92.3</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4075,77 +4204,75 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>372.2</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F43" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G43" s="10" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>19.8</v>
+        <v>236.3</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>88.7</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>26</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>99</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>29.1</v>
+        <v>24.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.5</v>
+        <v>23.8</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>30.4</v>
+        <v>29.3</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>27.8</v>
+        <v>24.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>84.7</v>
+        <v>23.5</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>9.1</v>
+        <v>88.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>96.59999999999999</v>
+      </c>
+      <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4160,77 +4287,75 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>365.9</v>
+        <v>32.2</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>32.6</v>
+        <v>29.9</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>26.9</v>
+        <v>25.6</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>11.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
+      </c>
+      <c r="K44" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>82.3</v>
+        <v>21.5</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>26.9</v>
+        <v>25.6</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>80</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.6</v>
+        <v>29.1</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>26.4</v>
+        <v>25.5</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>62</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>18.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>88.5</v>
+        <v>2.8</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>26.3</v>
+        <v>24.2</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>22.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>31.2</v>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4245,76 +4370,85 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>20.8</v>
+        <v>365.9</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>190.6</v>
+        <v>32.5</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>121.6</v>
+        <v>21.2</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="G45" s="10" t="n">
-        <v>69.09999999999999</v>
+        <v>26.9</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>1.3</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>18.8</v>
+        <v>49.4</v>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79727222
+785
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79272
+1
+77
+</t>
+        </is>
       </c>
       <c r="K45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="M45" s="3" t="n">
         <v>22.3</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>1825.9</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>5983.8</v>
+        <v>40</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>172.8</v>
+        <v>32.6</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>29.7</v>
+        <v>26.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>0.7</v>
+        <v>30.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>25.8</v>
+        <v>18.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>5.8</v>
+        <v>828.5</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>144.9</v>
+        <v>26.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>77.5</v>
+        <v>32.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>503.7</v>
+        <v>84.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>8</v>
+        <v>60.6</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4330,22 +4464,22 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>237.6</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G46" s="10" t="n">
-        <v>11.5</v>
+        <v>22.2</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>797.5</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>19.1</v>
+        <v>7.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>1.7</v>
@@ -4353,51 +4487,49 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n">
-        <v>21.1</v>
+      <c r="K46" s="3" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>84.8</v>
-      </c>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="n">
-        <v>99</v>
+        <v>593.8</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>28.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="Q46" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>21.8</v>
+        <v>79.7</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>29</v>
+        <v>72.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>75</v>
+        <v>7.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="W46" s="8" t="n">
-        <v>14.1</v>
-      </c>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="n">
-        <v>28.7</v>
+        <v>0.3</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,8 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -143,7 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -152,16 +158,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -778,7 +778,7 @@
         <v>186.2</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>20</v>
@@ -787,64 +787,62 @@
         <v>24.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>18.2</v>
+        <v>18.7</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>118.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>2.2</v>
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>23.4</v>
+        <v>20.1</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>83.40000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>28.2</v>
-      </c>
+        <v>10.2</v>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="8" t="n">
         <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X4" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X4" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>81.8</v>
+        <v>1811.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -860,7 +858,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>438.5</v>
+        <v>2903.8</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>32.6</v>
@@ -871,11 +869,11 @@
       <c r="F5" s="10" t="n">
         <v>25.4</v>
       </c>
-      <c r="G5" s="10" t="n">
-        <v>14.4</v>
+      <c r="G5" s="3" t="n">
+        <v>34.1</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6.2</v>
+        <v>16.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
@@ -884,52 +882,52 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.6</v>
+        <v>156.6</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>2.8</v>
+      <c r="V5" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="X5" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -945,60 +943,60 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.3</v>
+        <v>1422.3</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>34.2</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="G6" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G6" s="10" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>17.2</v>
+      <c r="H6" s="8" t="n">
+        <v>872.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>66</v>
+      <c r="M6" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>32.7</v>
+        <v>10</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="S6" s="3" t="n">
+      <c r="S6" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="U6" s="3" t="n">
+        <v>2929.8</v>
+      </c>
+      <c r="U6" s="8" t="n">
         <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
@@ -1011,10 +1009,10 @@
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1030,76 +1028,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4778.5</v>
+        <v>4785.1</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>24.7</v>
+        <v>34.7</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="G7" s="10" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>35.1</v>
+        <v>20.1</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="O7" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P7" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="P7" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>22.1</v>
+      <c r="R7" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="U7" s="3" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="U7" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="W7" s="3" t="n">
-        <v>84.09999999999999</v>
+      <c r="W7" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>27.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>66.2</v>
+        <v>166.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>438.5</v>
+        <v>13.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1115,67 +1113,67 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>299.6</v>
+        <v>1299</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>34.41</v>
+        <v>34.6</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="8" t="n">
         <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" s="8" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="N8" s="8" t="n">
-        <v>40.9</v>
+      <c r="N8" s="3" t="n">
+        <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q8" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>28</v>
+        <v>298</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>24.9</v>
+        <v>22.2</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>1.9</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>26.1</v>
@@ -1184,7 +1182,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1200,19 +1198,19 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.5</v>
-      </c>
-      <c r="D9" s="10" t="n">
+        <v>11783.5</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>164.8</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>130.8</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>67.90000000000001</v>
+      <c r="E9" s="9" t="n">
+        <v>196.9</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>1130.8</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>16.2</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
@@ -1221,22 +1219,22 @@
         <v>16.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>27.5</v>
+        <v>127.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>3.9</v>
+        <v>30.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>16.2</v>
+        <v>100.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>199.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>15.8</v>
+        <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>494.5</v>
+        <v>1494.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.2</v>
@@ -1248,32 +1246,28 @@
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>135.7</v>
+        <v>1135.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>116.8</v>
+        <v>1116.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>133.5</v>
+        <v>1133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>388.8</v>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222424272
-777
-</t>
-        </is>
+        <v>1388.8</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>141.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1304,7 +1298,7 @@
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
@@ -1312,15 +1306,9 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-2221
-</t>
-        </is>
-      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>19.9</v>
@@ -1332,37 +1320,37 @@
         <v>98.90000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q10" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q10" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>2.1</v>
+        <v>27.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>166</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>1.2</v>
+        <v>16.2</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W10" s="3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W10" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>272.8</v>
+        <v>79.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>41.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1378,7 +1366,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>265.6</v>
+        <v>1265.6</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>30.1</v>
@@ -1389,42 +1377,37 @@
       <c r="F11" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>1.3</v>
+      <c r="G11" s="10" t="n">
+        <v>10.3</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-505
-1799
-</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>927.3</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q11" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q11" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="R11" s="3" t="n">
@@ -1434,13 +1417,13 @@
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>720.6</v>
+        <v>170.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>2.1</v>
+      <c r="V11" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>24.9</v>
@@ -1449,14 +1432,10 @@
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-744
-</t>
-        </is>
+        <v>684</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>5.1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1472,7 +1451,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>342.4</v>
+        <v>247.1</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>31.8</v>
@@ -1486,32 +1465,32 @@
       <c r="G12" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.7</v>
+        <v>22.1</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.9</v>
+        <v>21.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>27.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>31.8</v>
@@ -1523,25 +1502,25 @@
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>57.8</v>
+        <v>59.8</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>1.8</v>
+        <v>19.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>24.6</v>
+        <v>27.9</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>284.6</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>7.7</v>
+        <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>57.2</v>
+        <v>181.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1557,34 +1536,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>428.6</v>
+        <v>1428.6</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>32.8</v>
+        <v>33.1</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>3.3</v>
+        <v>13.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>2.1</v>
+        <v>22.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>21.9</v>
@@ -1593,15 +1572,15 @@
         <v>26.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9.5</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>26.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1613,8 +1592,8 @@
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="3" t="n">
-        <v>28.6</v>
+      <c r="V13" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>24.8</v>
@@ -1623,10 +1602,10 @@
         <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>7.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>23.1</v>
+        <v>18.3</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1656,32 +1635,32 @@
       <c r="G14" s="10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>2.3</v>
+      <c r="H14" s="8" t="n">
+        <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J14" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>2.1</v>
-      </c>
       <c r="N14" s="3" t="n">
-        <v>26.4</v>
+        <v>264</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>197.3</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.4</v>
@@ -1689,29 +1668,29 @@
       <c r="R14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="S14" s="3" t="n">
+      <c r="S14" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W14" s="8" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="X14" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="X14" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>2.5</v>
+        <v>9.1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1727,31 +1706,31 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.6</v>
+        <v>359.6</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>32.5</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>1.7</v>
+      <c r="G15" s="10" t="n">
+        <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.4</v>
+        <v>18.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
@@ -1763,12 +1742,12 @@
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>1100</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="8" t="n">
         <v>32</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1778,7 +1757,7 @@
         <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>61.7</v>
+        <v>161.7</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>18.2</v>
@@ -1786,8 +1765,8 @@
       <c r="V15" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="3" t="n">
-        <v>4.8</v>
+      <c r="W15" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>28.8</v>
@@ -1796,7 +1775,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1812,57 +1791,43 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1591.2</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>1291.2</v>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>157.9</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>1317.2</v>
+      <c r="E16" s="9" t="n">
+        <v>1105.5</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>5131.7</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>929.2</v>
+        <v>99.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>11.5</v>
+        <v>111.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">790691
-22
-5682
-</t>
-        </is>
+      <c r="K16" s="3" t="n">
+        <v>36.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>10.6</v>
+        <v>1110.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">791727
-14
-000
-</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11722
-77218
-</t>
-        </is>
+        <v>109.5</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1130.7</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>27490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1871,47 +1836,31 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>121.9</v>
+        <v>1121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>136.1</v>
+        <v>1136.1</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>31.8</v>
+        <v>331.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7277978
-7566
-</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22414
-8711011466 7
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36595
-99781
-</t>
-        </is>
-      </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5555
-5721
-</t>
-        </is>
+        <v>176.6</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>1120.7</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <v>1407.4</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>741.1</v>
+        <v>34.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1927,7 +1876,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>38.2</v>
+        <v>1318.2</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>31.6</v>
@@ -1941,32 +1890,30 @@
       <c r="G17" s="10" t="n">
         <v>10.5</v>
       </c>
-      <c r="H17" s="8" t="n">
-        <v>292.8</v>
+      <c r="H17" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.3</v>
+        <v>12.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>36.8</v>
-      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M17" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M17" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>30.7</v>
+      <c r="N17" s="3" t="n">
+        <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>490.1</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>29.7</v>
@@ -1974,29 +1921,29 @@
       <c r="R17" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>2.2</v>
+      <c r="S17" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>6.4</v>
+        <v>166.4</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>33.7</v>
+        <v>26.7</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>42.5</v>
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>47.6</v>
+        <v>181.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2012,19 +1959,19 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>368</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>26.6</v>
+        <v>1368</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>28.61</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>16.9</v>
+        <v>10.9</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>20.4</v>
@@ -2032,31 +1979,23 @@
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-222
-</t>
-        </is>
+      <c r="J18" s="8" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>10.4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>24.4</v>
+        <v>21.4</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27844
-171719
-</t>
-        </is>
+      <c r="N18" s="8" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -2064,40 +2003,32 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="S18" s="3" t="n">
-        <v>7.7</v>
+      <c r="S18" s="8" t="n">
+        <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>58.5</v>
+        <v>98</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7444
-1779 7
-</t>
-        </is>
-      </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09442
-77 7
-</t>
-        </is>
+      <c r="V18" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>71.2</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>17.1</v>
+        <v>111</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2113,13 +2044,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>265.6</v>
+        <v>2260.6</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>30</v>
+        <v>30.4</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="F19" s="10" t="n">
         <v>26.5</v>
@@ -2127,32 +2058,32 @@
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>2.3</v>
+        <v>11.2</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>22.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>24.8</v>
+        <v>86.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>297.3</v>
+        <v>197.6</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>29.9</v>
@@ -2169,20 +2100,20 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="3" t="n">
-        <v>28.5</v>
+      <c r="V19" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>2.9</v>
+        <v>22.9</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>7218.7</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>3.3</v>
+        <v>78.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2201,28 +2132,28 @@
         <v>365.9</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>9.9</v>
+        <v>26.4</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>2.5</v>
+      <c r="I20" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>21.6</v>
@@ -2230,42 +2161,44 @@
       <c r="M20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>26.3</v>
+      <c r="N20" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="P20" s="3" t="n"/>
+        <v>98</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q20" s="3" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="R20" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>62.3</v>
+        <v>162.3</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>1.6</v>
+        <v>16.6</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>2.9</v>
+        <v>27.3</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>89</v>
+        <v>715</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2287,13 +2220,13 @@
         <v>30.6</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="F21" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="G21" s="10" t="n">
-        <v>9.5</v>
+      <c r="G21" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>19.6</v>
@@ -2305,22 +2238,22 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>2.6</v>
+        <v>10</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>986</v>
+        <v>199</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>6.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.6</v>
@@ -2332,25 +2265,25 @@
         <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>4.2</v>
+        <v>71.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>23.8</v>
+        <v>12.6</v>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>16.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>7.2</v>
+        <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2366,49 +2299,46 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>395.3</v>
-      </c>
-      <c r="D22" s="3" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>32.9</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="10" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="15" t="n">
-        <v>2</v>
+      <c r="F22" s="10" t="n">
+        <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>14.8</v>
+        <v>12.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>12.8</v>
+        <v>19.8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>4.3</v>
+        <v>14.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2.3</v>
+        <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>25.6</v>
+      <c r="N22" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68 2
-</t>
-        </is>
+        <v>97.5</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>32.4</v>
@@ -2419,29 +2349,26 @@
       <c r="S22" s="3" t="n">
         <v>89.3</v>
       </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65 2
-</t>
-        </is>
+      <c r="T22" s="3" t="n">
+        <v>160.5</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>27.8</v>
+        <v>26.8</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>84.90000000000001</v>
+      <c r="X22" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>72.3</v>
+        <v>186</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>4.9</v>
+        <v>14.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2457,62 +2384,43 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>739.6</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41444444
-1
-8684
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27955
-42
-12141
-</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-1141089
-</t>
-        </is>
+        <v>17439.6</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>1101.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>7.7</v>
+        <v>19.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>18.2</v>
+        <v>108.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>17</v>
+        <v>1107</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418686866
-50756012
-1441
-</t>
-        </is>
+        <v>1126.8</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>1489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
@@ -2524,28 +2432,28 @@
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>146.8</v>
+        <v>1146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>325.7</v>
+        <v>325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>86.5</v>
+        <v>134.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>24.6</v>
+        <v>120.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>2.7</v>
+        <v>140.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>860.6</v>
+        <v>2399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>3.7</v>
+        <v>36.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2561,84 +2469,74 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>739.6</v>
+        <v>347.9</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>7.2</v>
+        <v>31.6</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>21.4</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>1.8</v>
+        <v>26.5</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1.9</v>
+        <v>12.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>19.3</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>18.2</v>
+        <v>21.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6169690911
-2929
-</t>
-        </is>
+        <v>21.4</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>46.8</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>325.7</v>
+        <v>165.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74950
-448468
-</t>
-        </is>
+        <v>15.9</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>282.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>399</v>
+        <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7.3</v>
+        <v>17.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2654,77 +2552,73 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>34.9</v>
+        <v>106.7</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>31.6</v>
+        <v>26.4</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>21.5</v>
+        <v>20.7</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>26.4</v>
+        <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>19.3</v>
+        <v>23.7</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>21.6</v>
+        <v>22.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N25" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>264.4</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="n">
+        <v>244.1</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X25" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="O25" s="3" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X25" s="8" t="n">
-        <v>40.8</v>
-      </c>
       <c r="Y25" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>7.3</v>
-      </c>
+        <v>81.7</v>
+      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2739,92 +2633,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>16.7</v>
+        <v>290</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>26.4</v>
+        <v>37.2</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G26" s="10" t="n">
-        <v>5.7</v>
+        <v>29.1</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215852
-147
-</t>
-        </is>
+        <v>19.2</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-77
-</t>
-        </is>
+        <v>0.7</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>24.1</v>
+        <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>28.7</v>
+        <v>24.3</v>
+      </c>
+      <c r="R26" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>280.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>192</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>5.3</v>
+        <v>12.9</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7771717
-11811408 7
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>2.2</v>
+        <v>23.8</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>79.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-893
-</t>
-        </is>
+        <v>191.8</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2840,69 +2718,73 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>90</v>
+        <v>2322</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>4.1</v>
+        <v>25.5</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
+        <v>19.1</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L27" s="3" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.4</v>
+        <v>20.5</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="O27" s="3" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>198</v>
+      </c>
       <c r="P27" s="3" t="n">
-        <v>8</v>
+        <v>0.4</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>23.3</v>
+        <v>28.8</v>
+      </c>
+      <c r="R27" s="8" t="n">
+        <v>24.9</v>
       </c>
       <c r="S27" s="8" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>926</v>
+        <v>73.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2.4</v>
+        <v>10.5</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>23.8</v>
+        <v>26.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>26.8</v>
+        <v>24.4</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>3.8</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2917,80 +2799,74 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>322</v>
+        <v>1290.7</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>30.4</v>
+        <v>51.8</v>
       </c>
       <c r="E28" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-2923
-</t>
-        </is>
+      <c r="N28" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>297.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>16.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>29</v>
+        <v>31.2</v>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>73.2</v>
+        <v>160.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>26.9</v>
+        <v>18.1</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>2.8</v>
+        <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>27.1</v>
+        <v>28.4</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>81.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>2.4</v>
+        <v>10.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -3006,80 +2882,74 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>290.7</v>
+        <v>12146.8</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="n">
-        <v>1.9</v>
+        <v>11.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M29" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M29" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-2923
-</t>
-        </is>
+        <v>23.9</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>95.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>27.2</v>
+        <v>85.3</v>
+      </c>
+      <c r="R29" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>60.2</v>
+        <v>87</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>18.1</v>
+        <v>14.2</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>28.6</v>
+        <v>22.4</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>29.1</v>
+        <v>21.3</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>724.6</v>
+        <v>90.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>1.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3095,76 +2965,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>846.2</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>26</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>1</v>
+        <v>11056.2</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>1145.2</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>1103.2</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>14.2</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>12.2</v>
+        <v>196.6</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.6</v>
+        <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>8.4</v>
+        <v>38.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>21.1</v>
+        <v>1106.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>20.6</v>
+        <v>1105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>23.9</v>
+        <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>95.3</v>
+        <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>825.3</v>
+        <v>11135.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>23.6</v>
+        <v>120.1</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>28</v>
+        <v>1140.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>8</v>
+        <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>4.1</v>
+        <v>18.5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>2.4</v>
+        <v>1126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>24.6</v>
+        <v>1115.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>2.4</v>
+        <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>4.2</v>
+        <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>1.3</v>
+        <v>21.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3180,76 +3050,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>452.1</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F31" s="14" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>38.8</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>15.1</v>
+        <v>21.3</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>487.6</v>
+        <v>97.5</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>35.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="R31" s="8" t="n">
-        <v>280.7</v>
-      </c>
-      <c r="S31" s="8" t="n">
-        <v>40.9</v>
+        <v>24.1</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>396.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>81.5</v>
+        <v>88.8</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>26.1</v>
+        <v>25.2</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>21.3</v>
+        <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>4.6</v>
+        <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>44.2</v>
+        <v>24.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>2.5</v>
+        <v>145.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3265,74 +3133,72 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>211.2</v>
+        <v>384.7</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>29</v>
+        <v>31.1</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>20.6</v>
+        <v>19.3</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H32" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="Z32" s="3" t="n">
         <v>19.3</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="W32" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>5.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3348,74 +3214,72 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>384.7</v>
+        <v>213.3</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>31.1</v>
+        <v>29.2</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>18</v>
+        <v>24.4</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.4</v>
+        <v>11</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>23.3</v>
-      </c>
+        <v>21.4</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>10</v>
+        <v>299</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>2.5</v>
+        <v>28.9</v>
+      </c>
+      <c r="R33" s="8" t="n">
+        <v>206.6</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>61</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y33" s="3" t="n"/>
+        <v>16.5</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X33" s="3" t="inlineStr"/>
+      <c r="Y33" s="3" t="n">
+        <v>861.4</v>
+      </c>
       <c r="Z33" s="3" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3431,72 +3295,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>213.3</v>
+        <v>311.6</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>29.2</v>
+        <v>31.9</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>19.6</v>
+        <v>21.5</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>24.4</v>
+        <v>26.7</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>21.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="L34" s="8" t="n">
+        <v>21.8</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>992.6</v>
+        <v>199</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>28.9</v>
+        <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>4.6</v>
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>30.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>2720.9</v>
+        <v>169.4</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>11.5</v>
+        <v>13.3</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>25.6</v>
+        <v>27.3</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="X34" s="3" t="n"/>
-      <c r="Y34" s="3" t="n"/>
+        <v>24.8</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>82.8</v>
+      </c>
       <c r="Z34" s="3" t="n">
-        <v>2.3</v>
+        <v>16.5</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3512,88 +3380,76 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>311.6</v>
+        <v>353.4</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>31.9</v>
+        <v>31.1</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>1.5</v>
+        <v>25.9</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>10.3</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-9217
-</t>
-        </is>
+        <v>19.7</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="L35" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>197.2</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>1614.3</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="V35" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>996</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242461
-289
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26282
-79794
-</t>
-        </is>
+      <c r="W35" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>4.5</v>
+        <v>18.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3609,76 +3465,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>353.4</v>
+        <v>430.7</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>31</v>
+        <v>32.1</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>25.9</v>
+        <v>26.5</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H36" s="3" t="n"/>
+        <v>11.2</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="I36" s="3" t="n">
-        <v>22.4</v>
+        <v>2.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>14.4</v>
+      </c>
+      <c r="K36" s="8" t="n">
+        <v>30.6</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>21.3</v>
+        <v>21</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>20.1</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>25.1</v>
+        <v>26.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>97.2</v>
+        <v>918.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.7</v>
+        <v>10.6</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>31.1</v>
+        <v>32.1</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>24.9</v>
+        <v>26</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>27.5</v>
+        <v>29.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>6.3</v>
+        <v>62.2</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17.4</v>
+        <v>18</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>27.8</v>
+        <v>28.7</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242461
-289
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="3" t="n"/>
+        <v>24.6</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>42.4</v>
+      </c>
       <c r="Z36" s="3" t="n">
-        <v>8.4</v>
+        <v>211</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3694,70 +3550,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>430.7</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G37" s="3" t="n"/>
+        <v>1693.7</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>1155.4</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>1102</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>53.4</v>
+      </c>
       <c r="H37" s="3" t="n">
-        <v>13.8</v>
+        <v>96.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>2.4</v>
+        <v>110.1</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>4.4</v>
+        <v>18.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>30.6</v>
+        <v>135.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>21</v>
+        <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>20.7</v>
+        <v>1803.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>242.8</v>
+        <v>121.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>9.5</v>
+        <v>492.9</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>32.1</v>
+        <v>143.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>26</v>
+        <v>1126.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>29.7</v>
+        <v>1143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>62.2</v>
+        <v>13821.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>18.4</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>28.7</v>
+        <v>136.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="X37" s="3" t="n"/>
-      <c r="Y37" s="3" t="n"/>
+        <v>121.6</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>1142.4</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>398.2</v>
+      </c>
       <c r="Z37" s="3" t="n">
-        <v>7909.7</v>
+        <v>1392.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3773,83 +3635,75 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>693.7</v>
+        <v>338.7</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>55.4</v>
+        <v>31</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2</v>
+        <v>20.4</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>28.7</v>
+        <v>25.7</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>53.4</v>
+        <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>96.5</v>
+        <v>19.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">887 1
-18 74
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>35.6</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>185.8</v>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42477
-114111
-</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24268701
-6888
-</t>
-        </is>
+        <v>21.2</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>53.7</v>
+        <v>10.3</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="R38" s="8" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="S38" s="8" t="n">
-        <v>43.1</v>
+        <v>25.2</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>324.8</v>
+        <v>169</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>77.7</v>
+        <v>13.5</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X38" s="3" t="n"/>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="n"/>
+        <v>87.40000000000001</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3864,78 +3718,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H39" s="3" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>20.6</v>
+        <v>1.7</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="N39" s="8" t="n">
-        <v>24.1</v>
+      <c r="M39" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>492.7</v>
+        <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.3</v>
+        <v>10.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>28.6</v>
+        <v>31.9</v>
+      </c>
+      <c r="R39" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>65</v>
+        <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="W39" s="8" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-1
-</t>
-        </is>
+        <v>17.3</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>288.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>2.9</v>
+        <v>13.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3951,76 +3801,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>32.5</v>
+        <v>1453.1</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>31.9</v>
+        <v>32.9</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>20.3</v>
+        <v>18.9</v>
       </c>
       <c r="F40" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>1797.8</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="R40" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="G40" s="10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="N40" s="3" t="n">
+      <c r="S40" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="O40" s="3" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="T40" s="3" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>24.3</v>
+      <c r="W40" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>2.5</v>
+        <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>88.2</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0.8</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -4036,74 +3886,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>453.7</v>
-      </c>
-      <c r="D41" s="15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>4.1</v>
+        <v>269.6</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>43.6</v>
       </c>
       <c r="L41" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M41" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>19.6</v>
-      </c>
       <c r="N41" s="3" t="n">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>97.8</v>
+        <v>199</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.5</v>
+        <v>10.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>66</v>
+        <v>22.3</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>29.3</v>
+        <v>24.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>59.2</v>
+        <v>192.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="Y41" s="3" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>816.6</v>
+      </c>
+      <c r="W41" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>190.5</v>
+      </c>
       <c r="Z41" s="3" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4119,77 +3971,75 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>26.5</v>
+        <v>1236.3</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>19.6</v>
+        <v>20.2</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="I42" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J42" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K42" s="3" t="n">
-        <v>4.6</v>
+        <v>28.1</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>19.9</v>
+        <v>21.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>23</v>
+        <v>21.8</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P42" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>24.9</v>
+        <v>199</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q42" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="R42" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>92.3</v>
+        <v>197.7</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>23.4</v>
+        <v>21.7</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>23.5</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>190.6</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4204,75 +4054,77 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>236.3</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>1.3</v>
+        <v>372.2</v>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>20.6</v>
+        <v>19.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>6.7</v>
+        <v>12</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>88.7</v>
+        <v>10</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>26</v>
+        <v>25.6</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>199</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>24.1</v>
+        <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>23.8</v>
+        <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>29.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>97.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="V43" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="W43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W43" s="3" t="n">
-        <v>23.5</v>
-      </c>
       <c r="X43" s="3" t="n">
-        <v>88.2</v>
+        <v>29.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4287,75 +4139,77 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>32.2</v>
+        <v>365.9</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>29.9</v>
+        <v>32.5</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>25.6</v>
+        <v>26.9</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>19.8</v>
+        <v>11.3</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K44" s="8" t="n">
-        <v>6</v>
+        <v>19.6</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>21.6</v>
+        <v>28.3</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>25.6</v>
+        <v>22.3</v>
+      </c>
+      <c r="N44" s="8" t="n">
+        <v>26.9</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>99</v>
+        <v>1100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>29.1</v>
+        <v>32.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>25.5</v>
+        <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>162</v>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>2.8</v>
+        <v>28.5</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>1.1</v>
+        <v>26.3</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>32.2</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>166</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4369,86 +4223,65 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>365.9</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="G45" s="3" t="n">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="12" t="inlineStr"/>
+      <c r="E45" s="9" t="n">
+        <v>1121</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>1796.1</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>1166.9</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="H45" s="3" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79727222
-785
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79272
-1
-77
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3" t="n">
-        <v>32.6</v>
+        <v>1752.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>149.1</v>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
       <c r="U45" s="3" t="n">
-        <v>18.6</v>
+        <v>168.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>828.5</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>32.8</v>
-      </c>
+        <v>138.1</v>
+      </c>
+      <c r="W45" s="3" t="inlineStr"/>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>84.8</v>
+        <v>3503.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>60.6</v>
+        <v>9316</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4464,72 +4297,74 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>797.5</v>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>2337.6</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>11.5</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>7.7</v>
+        <v>19.1</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>98.3</v>
-      </c>
+        <v>53.1</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="8" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="N46" s="3" t="n"/>
+        <v>11.1</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>24.8</v>
+      </c>
       <c r="O46" s="3" t="n">
-        <v>593.8</v>
+        <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q46" s="8" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>72.7</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>7.7</v>
+        <v>729</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="W46" s="3" t="n"/>
+        <v>643.4</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>24.1</v>
+      </c>
       <c r="X46" s="3" t="n">
-        <v>0.3</v>
+        <v>28.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>23.7</v>
+        <v>283.9</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>2</v>
+        <v>15.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,7 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,10 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -775,74 +766,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>186.2</v>
+        <v>136.2</v>
       </c>
       <c r="D4" s="10" t="n">
         <v>28.1</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="F4" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>118.2</v>
+        <v>81.7</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>83.40000000000001</v>
+      <c r="N4" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q4" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>28.8</v>
+      </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>27.1</v>
+      <c r="S4" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X4" s="8" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1811.8</v>
+        <v>181.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -858,7 +851,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2903.8</v>
+        <v>203.8</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>32.6</v>
@@ -869,8 +862,8 @@
       <c r="F5" s="10" t="n">
         <v>25.4</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>34.1</v>
+      <c r="G5" s="10" t="n">
+        <v>14.4</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.8</v>
@@ -882,52 +875,52 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>199</v>
+        <v>909</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>156.6</v>
+        <v>56.6</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X5" s="8" t="n">
-        <v>27.8</v>
+      <c r="X5" s="11" t="n">
+        <v>72.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>11</v>
+        <v>141.1</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -943,7 +936,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1422.3</v>
+        <v>122.3</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>34.2</v>
@@ -957,8 +950,8 @@
       <c r="G6" s="10" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>872.6</v>
+      <c r="H6" s="11" t="n">
+        <v>184.6</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>14.6</v>
@@ -967,7 +960,7 @@
         <v>7.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20</v>
@@ -981,38 +974,38 @@
       <c r="O6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" s="8" t="n">
-        <v>21.7</v>
+      <c r="P6" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>32.7</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="S6" s="8" t="n">
+      <c r="S6" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>2929.8</v>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v>20.7</v>
+        <v>22.8</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>23.7</v>
+      <c r="W6" s="11" t="n">
+        <v>31.7</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>166.4</v>
+        <v>16614.1</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1028,16 +1021,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4785.1</v>
+        <v>6472.5</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>34.7</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>19.9</v>
+        <v>7.3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>27.3</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1046,13 +1039,13 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>4.3</v>
+        <v>47.9</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7.9</v>
+        <v>1.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>20.1</v>
@@ -1067,37 +1060,37 @@
         <v>100</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S7" s="8" t="n">
+      <c r="R7" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="U7" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="11" t="n">
         <v>29.5</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>166.2</v>
+        <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1113,7 +1106,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1299</v>
+        <v>299</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>34.6</v>
@@ -1127,59 +1120,59 @@
       <c r="G8" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>19</v>
+      <c r="H8" s="11" t="n">
+        <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="8" t="n">
-        <v>1.9</v>
+      <c r="W8" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>20.6</v>
@@ -1198,28 +1191,28 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>11783.5</v>
+        <v>1781.2</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>164.8</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>196.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1130.8</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>16.2</v>
+        <v>1301.7</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>65.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>127.5</v>
+        <v>12.8</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>30.9</v>
@@ -1228,31 +1221,31 @@
         <v>100.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>199.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1494.5</v>
+        <v>894.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>149.6</v>
+        <v>1179.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>121.9</v>
+        <v>122.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1135.7</v>
+        <v>155.1</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
@@ -1261,10 +1254,10 @@
         <v>1116.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>1133.5</v>
+        <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1388.8</v>
+        <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>141.6</v>
@@ -1283,7 +1276,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
+        <v>8188.5</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>33</v>
@@ -1298,16 +1291,16 @@
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M10" s="3" t="n">
@@ -1322,17 +1315,17 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="8" t="n">
-        <v>24.4</v>
+      <c r="R10" s="3" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.1</v>
+        <v>27.8</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>16.2</v>
@@ -1340,17 +1333,17 @@
       <c r="V10" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>26.7</v>
+      <c r="X10" s="11" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>79.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1369,10 +1362,10 @@
         <v>1265.6</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>24.9</v>
@@ -1384,28 +1377,28 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>24.5</v>
+      <c r="N11" s="3" t="n">
+        <v>24.3</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>927.3</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>29.9</v>
@@ -1413,29 +1406,29 @@
       <c r="R11" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="S11" s="11" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>170.6</v>
+        <v>720.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>24.9</v>
+      <c r="V11" s="11" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="W11" s="11" t="n">
+        <v>16.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>684</v>
+        <v>2894</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>5.1</v>
+        <v>11.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1451,46 +1444,46 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>247.1</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F12" s="10" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>22.1</v>
+      <c r="I12" s="11" t="n">
+        <v>227.1</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>21.9</v>
+      <c r="M12" s="11" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>17.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>27.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>31.8</v>
@@ -1499,19 +1492,19 @@
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>27.1</v>
+        <v>21.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>59.8</v>
+        <v>51.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>284.6</v>
+        <v>21.9</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>28.8</v>
@@ -1520,7 +1513,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>181.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1536,31 +1529,31 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1428.6</v>
+        <v>428.6</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>33.1</v>
+        <v>32.8</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="10" t="n">
         <v>12.4</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>13.3</v>
+        <v>18.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>22.1</v>
@@ -1580,32 +1573,32 @@
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="8" t="n">
+      <c r="R13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>25.8</v>
+      <c r="S13" s="11" t="n">
+        <v>21.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>52.7</v>
+        <v>427.4</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>28</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1635,7 +1628,7 @@
       <c r="G14" s="10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1644,9 +1637,7 @@
       <c r="J14" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K14" s="8" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="K14" s="3" t="inlineStr"/>
       <c r="L14" s="3" t="n">
         <v>22.4</v>
       </c>
@@ -1654,25 +1645,25 @@
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>264</v>
+        <v>26.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>197.3</v>
+        <v>97.3</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>22.4</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>2.9</v>
@@ -1680,17 +1671,17 @@
       <c r="V14" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="X14" s="8" t="n">
+      <c r="W14" s="11" t="n">
+        <v>211.6</v>
+      </c>
+      <c r="X14" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1706,16 +1697,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>359.6</v>
+        <v>282.8</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>11.7</v>
@@ -1724,30 +1715,30 @@
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>25.1</v>
+      <c r="K15" s="11" t="n">
+        <v>51.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="11" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3" t="n">
         <v>32</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1757,7 +1748,7 @@
         <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>161.7</v>
+        <v>61.7</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>18.2</v>
@@ -1765,17 +1756,17 @@
       <c r="V15" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="8" t="n">
+      <c r="W15" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>738.1</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>10.1</v>
+        <v>100.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1794,13 +1785,13 @@
         <v>1291.2</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>157.9</v>
+        <v>167.9</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1105.5</v>
+        <v>105.5</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>5131.7</v>
+        <v>151.4</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
@@ -1809,7 +1800,7 @@
         <v>99.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>111.5</v>
+        <v>11.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.4</v>
@@ -1824,10 +1815,10 @@
         <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1130.7</v>
+        <v>1230.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>27490.1</v>
+        <v>2490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1836,28 +1827,28 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1121.9</v>
+        <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.1</v>
+        <v>1136.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>133.7</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1120.7</v>
+        <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>162.5</v>
+        <v>142.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1407.4</v>
+        <v>1407.6</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>34.4</v>
@@ -1876,16 +1867,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1318.2</v>
+        <v>318.2</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>21.1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>10.5</v>
@@ -1899,48 +1890,50 @@
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
+        <v>398</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>29.7</v>
+        <v>29.1</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S17" s="8" t="n">
-        <v>28.2</v>
+      <c r="S17" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>28.5</v>
+        <v>15.8</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" s="11" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="X17" s="11" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>181.5</v>
+        <v>81.5</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>16.9</v>
@@ -1959,31 +1952,31 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1368</v>
-      </c>
-      <c r="D18" s="13" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>28.61</v>
-      </c>
-      <c r="G18" s="3" t="n">
+        <v>368</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G18" s="10" t="n">
         <v>10.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>20.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>10.4</v>
+      <c r="J18" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>6.4</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>21.4</v>
@@ -1991,11 +1984,11 @@
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="8" t="n">
-        <v>224.8</v>
+      <c r="N18" s="11" t="n">
+        <v>12.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>97.3</v>
+        <v>91.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -2003,29 +1996,29 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="V18" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>111</v>
@@ -2044,55 +2037,55 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2260.6</v>
+        <v>265.6</v>
       </c>
       <c r="D19" s="10" t="n">
         <v>30.4</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G19" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G19" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L19" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>86.3</v>
+        <v>26.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>197.6</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q19" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="Q19" s="11" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>31.1</v>
+        <v>51.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>73.7</v>
@@ -2100,20 +2093,20 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="8" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X19" s="8" t="n">
-        <v>71.09999999999999</v>
+      <c r="V19" s="11" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="W19" s="11" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>89</v>
+        <v>829</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>78.3</v>
+        <v>185.9</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2129,13 +2122,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>365.9</v>
+        <v>3865.9</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>26.4</v>
@@ -2146,8 +2139,8 @@
       <c r="H20" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>28.1</v>
+      <c r="I20" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>14.5</v>
@@ -2161,26 +2154,26 @@
       <c r="M20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N20" s="8" t="n">
-        <v>35.4</v>
+      <c r="N20" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98</v>
+        <v>928</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="R20" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R20" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>162.3</v>
+        <v>12.3</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>16.6</v>
@@ -2188,14 +2181,14 @@
       <c r="V20" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="W20" s="8" t="n">
-        <v>23.8</v>
+      <c r="W20" s="11" t="n">
+        <v>28.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>27.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>715</v>
+        <v>125</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>19.1</v>
@@ -2225,8 +2218,8 @@
       <c r="F21" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>29.5</v>
+      <c r="G21" s="10" t="n">
+        <v>9.5</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>19.6</v>
@@ -2238,22 +2231,22 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>18.6</v>
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.6</v>
+        <v>23.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.6</v>
@@ -2262,7 +2255,7 @@
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>31.2</v>
+        <v>91.2</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>71.2</v>
@@ -2270,20 +2263,20 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="8" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="W21" s="8" t="n">
-        <v>16.6</v>
+      <c r="V21" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W21" s="11" t="n">
+        <v>46.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>77.3</v>
+        <v>712.3</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2317,21 +2310,21 @@
         <v>19.8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N22" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="N22" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
@@ -2350,25 +2343,25 @@
         <v>89.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>26.8</v>
+        <v>86.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X22" s="8" t="n">
-        <v>29.1</v>
+      <c r="X22" s="11" t="n">
+        <v>29.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>14.9</v>
+        <v>1244.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2384,31 +2377,31 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>17439.6</v>
+        <v>8519.6</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>164.5</v>
+        <v>1468.5</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>107.2</v>
+        <v>1074.2</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>132.4</v>
       </c>
-      <c r="G23" s="13" t="n">
-        <v>25</v>
+      <c r="G23" s="3" t="n">
+        <v>50.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1101.8</v>
+        <v>101.8</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>19.3</v>
+        <v>104.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>19.3</v>
+        <v>495.1</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>108.2</v>
@@ -2417,31 +2410,31 @@
         <v>1107</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1126.8</v>
+        <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1489.4</v>
+        <v>489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>155.7</v>
+        <v>1565.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1146.8</v>
+        <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>325.1</v>
+        <v>3325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>134.4</v>
+        <v>138.4</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>120.3</v>
@@ -2450,10 +2443,10 @@
         <v>140.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>2399</v>
+        <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>36.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2469,16 +2462,16 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>347.9</v>
+        <v>343.9</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>31.6</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="G24" s="10" t="n">
         <v>10.1</v>
@@ -2492,21 +2485,23 @@
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <v>22.4</v>
+      <c r="N24" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>31.1</v>
@@ -2515,10 +2510,10 @@
         <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>29.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>165.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
@@ -2526,17 +2521,17 @@
       <c r="V24" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="8" t="n">
+      <c r="W24" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X24" s="8" t="n">
-        <v>282.2</v>
+      <c r="X24" s="11" t="n">
+        <v>29.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>17.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2555,16 +2550,16 @@
         <v>106.7</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="F25" s="10" t="n">
         <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.2</v>
@@ -2576,7 +2571,7 @@
         <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>22.4</v>
@@ -2585,38 +2580,38 @@
         <v>22.1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>264.4</v>
+        <v>26.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>97</v>
+        <v>914</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="8" t="n">
-        <v>284.1</v>
-      </c>
-      <c r="S25" s="8" t="n">
+      <c r="R25" s="3" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="S25" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
-        <v>244.1</v>
-      </c>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="V25" s="3" t="inlineStr"/>
       <c r="W25" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="11" t="n">
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>81.7</v>
+        <v>8417.4</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2635,29 +2630,29 @@
       <c r="C26" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>29.1</v>
+      <c r="D26" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>14.1</v>
+        <v>12.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>10.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>21.4</v>
@@ -2666,28 +2661,28 @@
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>280.9</v>
+      <c r="R26" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>23.8</v>
@@ -2695,14 +2690,14 @@
       <c r="W26" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X26" s="8" t="n">
-        <v>79.09999999999999</v>
+      <c r="X26" s="11" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.4</v>
+        <v>124.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2718,16 +2713,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2322</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E27" s="10" t="n">
+        <v>322</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>25.5</v>
+      <c r="F27" s="12" t="n">
+        <v>35.4</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>19.9</v>
@@ -2738,12 +2733,14 @@
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>20.7</v>
+        <v>50.3</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
@@ -2752,7 +2749,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2760,31 +2757,33 @@
       <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="8" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S27" s="8" t="n">
-        <v>89</v>
+      <c r="R27" s="11" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>73.2</v>
+        <v>23.2</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>26.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X27" s="8" t="n">
-        <v>29</v>
+        <v>94.40000000000001</v>
+      </c>
+      <c r="X27" s="11" t="n">
+        <v>289</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2799,21 +2798,23 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1290.7</v>
+        <v>290.7</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>51.8</v>
+        <v>31.7</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>20.5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="G28" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G28" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="I28" s="3" t="n">
         <v>2.2</v>
       </c>
@@ -2821,39 +2822,39 @@
         <v>3.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N28" s="8" t="n">
+      <c r="N28" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>297.3</v>
+        <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>160.2</v>
+        <v>60.2</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="8" t="n">
+      <c r="V28" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2866,7 +2867,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>10.7</v>
+        <v>107.4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2882,26 +2883,28 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12146.8</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E29" s="10" t="n">
+        <v>246.8</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
+      <c r="F29" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="I29" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8.4</v>
@@ -2909,7 +2912,7 @@
       <c r="L29" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2922,16 +2925,16 @@
         <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="R29" s="8" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="R29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="S29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>87</v>
+        <v>821</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>14.2</v>
@@ -2942,14 +2945,14 @@
       <c r="W29" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>14.6</v>
+      <c r="X29" s="11" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>90.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2967,17 +2970,17 @@
       <c r="C30" s="3" t="n">
         <v>11056.2</v>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="10" t="n">
         <v>1145.2</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="10" t="n">
         <v>1103.2</v>
       </c>
-      <c r="F30" s="9" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="G30" s="13" t="n">
-        <v>14.2</v>
+      <c r="F30" s="10" t="n">
+        <v>1124.2</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>196.6</v>
@@ -2989,52 +2992,52 @@
         <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>38.8</v>
+        <v>28.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>1106.5</v>
+        <v>106.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1105.2</v>
+        <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>123.9</v>
+        <v>125.9</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>11135.8</v>
+        <v>1135.8</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>120.1</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1140.9</v>
+        <v>140.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>1126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>1115.9</v>
+        <v>115.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>135.9</v>
+        <v>132.9</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>21.8</v>
+        <v>28.1</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3052,16 +3055,16 @@
       <c r="C31" s="3" t="n">
         <v>211.2</v>
       </c>
-      <c r="D31" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G31" s="10" t="n">
+      <c r="D31" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G31" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3073,26 +3076,28 @@
       <c r="J31" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="N31" s="8" t="n">
+      <c r="M31" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="N31" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.5</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3101,23 +3106,23 @@
       <c r="T31" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="U31" s="8" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="V31" s="8" t="n">
+      <c r="U31" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>27.2</v>
+        <v>97.2</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>145.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3133,7 +3138,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>384.7</v>
+        <v>8816.9</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>31.1</v>
@@ -3147,17 +3152,17 @@
       <c r="G32" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="11" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>12.3</v>
+        <v>2.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.1</v>
@@ -3165,9 +3170,11 @@
       <c r="M32" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>23.9</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0</v>
@@ -3175,17 +3182,17 @@
       <c r="Q32" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>27.5</v>
+      <c r="S32" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>18.5</v>
+        <v>61</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>27.4</v>
@@ -3193,9 +3200,11 @@
       <c r="W32" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="n">
+        <v>97.2</v>
+      </c>
       <c r="Y32" s="3" t="n">
-        <v>174.6</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>19.3</v>
@@ -3225,61 +3234,65 @@
       <c r="F33" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
+      <c r="G33" s="10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>21.5</v>
+        <v>14.8</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>81.5</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>206.6</v>
-      </c>
-      <c r="S33" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="X33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="n">
+        <v>28.3</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>861.4</v>
+        <v>86.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3301,13 +3314,13 @@
         <v>31.9</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="F34" s="10" t="n">
         <v>26.7</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>20.2</v>
@@ -3316,12 +3329,12 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.5</v>
+        <v>39.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3331,22 +3344,22 @@
         <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>30.5</v>
+        <v>3</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>25.8</v>
+        <v>23.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>169.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>13.3</v>
@@ -3361,7 +3374,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3401,55 +3414,55 @@
         <v>2.4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>197.2</v>
+        <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="8" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="S35" s="8" t="n">
+      <c r="R35" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S35" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>1614.3</v>
+        <v>61.3</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="V35" s="8" t="n">
+      <c r="V35" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>19.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>18.4</v>
+        <v>811.1</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3486,25 +3499,25 @@
         <v>2.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K36" s="8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K36" s="3" t="n">
         <v>30.6</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="8" t="n">
-        <v>20.1</v>
+      <c r="M36" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>26.2</v>
+        <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>918.5</v>
+        <v>98.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>32.1</v>
@@ -3527,14 +3540,14 @@
       <c r="W36" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>28.3</v>
+      <c r="X36" s="11" t="n">
+        <v>83.90000000000001</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>42.4</v>
+        <v>172</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>211</v>
+        <v>11</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3552,11 +3565,11 @@
       <c r="C37" s="3" t="n">
         <v>1693.7</v>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>1155.4</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>1102</v>
+      <c r="D37" s="10" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>102</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>128.7</v>
@@ -3574,52 +3587,52 @@
         <v>18.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>135.6</v>
+        <v>35.6</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1803.2</v>
+        <v>105.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>121.1</v>
+        <v>126.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>492.9</v>
+        <v>492.7</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.7</v>
+        <v>17.1</v>
       </c>
       <c r="Q37" s="3" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
         <v>143.1</v>
       </c>
-      <c r="R37" s="3" t="n">
-        <v>1126.2</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>1143.1</v>
-      </c>
       <c r="T37" s="3" t="n">
-        <v>13821.8</v>
+        <v>8216.799999999999</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>136.8</v>
+        <v>126.8</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>1142.4</v>
+        <v>102.4</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>1392.7</v>
+        <v>892.1</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3650,10 +3663,10 @@
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.6</v>
@@ -3672,37 +3685,37 @@
         <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="R38" s="8" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="R38" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="V38" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V38" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>26.3</v>
+        <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>28.5</v>
+        <v>88.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2.9</v>
+        <v>566.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3718,21 +3731,21 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="E39" s="10" t="n">
+        <v>3232.5</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>821.8100000000001</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F39" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+      <c r="G39" s="11" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3741,11 +3754,13 @@
       <c r="J39" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="8" t="n">
+      <c r="K39" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L39" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3755,37 +3770,37 @@
         <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>126</v>
-      </c>
-      <c r="S39" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="R39" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="S39" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>24.9</v>
+        <v>11.9</v>
+      </c>
+      <c r="V39" s="11" t="n">
+        <v>49.1</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>27.6</v>
+        <v>2.7</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>288.2</v>
+        <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>13.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3801,13 +3816,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1453.1</v>
+        <v>1534.1</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="F40" s="10" t="n">
         <v>25.9</v>
@@ -3819,33 +3834,33 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12.7</v>
+        <v>2.1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>28.6</v>
+        <v>22.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>1797.8</v>
+        <v>97.8</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3858,19 +3873,19 @@
         <v>20.2</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W40" s="8" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W40" s="11" t="n">
         <v>23.8</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>22.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>101.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3886,7 +3901,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>269.6</v>
+        <v>965.6</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>31.6</v>
@@ -3909,8 +3924,8 @@
       <c r="J41" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K41" s="8" t="n">
-        <v>43.6</v>
+      <c r="K41" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.9</v>
@@ -3922,10 +3937,10 @@
         <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>22.3</v>
@@ -3937,25 +3952,25 @@
         <v>24.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>192.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>816.6</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="X41" s="8" t="n">
-        <v>28</v>
+        <v>2.8</v>
+      </c>
+      <c r="V41" s="11" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X41" s="11" t="n">
+        <v>9218</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>190.5</v>
+        <v>90.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.9</v>
+        <v>18.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3971,10 +3986,10 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1236.3</v>
+        <v>836.3</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>20.2</v>
@@ -3989,12 +4004,12 @@
         <v>20</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K42" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K42" s="11" t="n">
         <v>28.1</v>
       </c>
       <c r="L42" s="3" t="n">
@@ -4003,43 +4018,45 @@
       <c r="M42" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="N42" s="8" t="n">
-        <v>26</v>
+      <c r="N42" s="3" t="n">
+        <v>26.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>199</v>
+        <v>1899</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="8" t="n">
+      <c r="Q42" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="R42" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>197.7</v>
+        <v>97.7</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W42" s="8" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>28.2</v>
+        <v>0.8</v>
+      </c>
+      <c r="V42" s="11" t="n">
+        <v>822.9</v>
+      </c>
+      <c r="W42" s="11" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="X42" s="11" t="n">
+        <v>88.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>190.6</v>
-      </c>
-      <c r="Z42" s="3" t="inlineStr"/>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4057,10 +4074,10 @@
         <v>372.2</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>25.6</v>
@@ -4072,13 +4089,13 @@
         <v>19.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>3.7</v>
+        <v>13.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.6</v>
@@ -4090,7 +4107,7 @@
         <v>25.6</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>0.2</v>
@@ -4099,22 +4116,22 @@
         <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>24.7</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W43" s="11" t="n">
+        <v>41.4</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>29.1</v>
@@ -4123,7 +4140,7 @@
         <v>18</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>18.2</v>
+        <v>198.2</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4139,7 +4156,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>365.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>32.5</v>
@@ -4153,47 +4170,47 @@
       <c r="G44" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="8" t="n">
-        <v>19.4</v>
+      <c r="H44" s="3" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>28.3</v>
+        <v>22.3</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="11" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>30.1</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="U44" s="8" t="n">
-        <v>18.6</v>
+      <c r="U44" s="3" t="n">
+        <v>8.6</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>28.5</v>
@@ -4201,14 +4218,14 @@
       <c r="W44" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>32.2</v>
+      <c r="X44" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4223,65 +4240,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="12" t="inlineStr"/>
+      <c r="C45" s="3" t="n">
+        <v>2026.2</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>19165.6</v>
+      </c>
       <c r="E45" s="9" t="n">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1796.1</v>
-      </c>
-      <c r="G45" s="13" t="n">
-        <v>10.9</v>
+        <v>2026.1</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>9.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>114.7</v>
+        <v>1114.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>10.7</v>
+        <v>1101</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>18.4</v>
+        <v>118.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>172.3</v>
+        <v>743.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1166.9</v>
+        <v>11665.9</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>122.9</v>
+        <v>128.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>148.7</v>
+        <v>1148.8</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>293.8</v>
+        <v>292.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1752.8</v>
+        <v>172.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr"/>
+        <v>1469.1</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>174.1</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>1450.8</v>
+      </c>
       <c r="U45" s="3" t="n">
-        <v>168.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+        <v>158.1</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>84.5</v>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>3503.7</v>
+        <v>900.1</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>9316</v>
+        <v>56</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4297,19 +4326,19 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2337.6</v>
+        <v>237.6</v>
       </c>
       <c r="D46" s="10" t="n">
         <v>31.8</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>20.9</v>
+        <v>20.3</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G46" s="8" t="n">
-        <v>11.5</v>
+        <v>26</v>
+      </c>
+      <c r="G46" s="11" t="n">
+        <v>21.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>19.1</v>
@@ -4318,13 +4347,15 @@
         <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="11" t="n">
         <v>11.1</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4334,37 +4365,37 @@
         <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="8" t="n">
-        <v>216.8</v>
-      </c>
-      <c r="S46" s="8" t="n">
+      <c r="R46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>729</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="8" t="n">
-        <v>643.4</v>
-      </c>
-      <c r="W46" s="8" t="n">
+      <c r="V46" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>283.9</v>
+        <v>83.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>15.7</v>
+        <v>62.5</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -140,16 +140,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -766,25 +772,25 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>136.2</v>
+        <v>186.2</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="F4" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>81.7</v>
+        <v>87.2</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2.9</v>
@@ -808,13 +814,13 @@
         <v>0.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>22.1</v>
+        <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
@@ -826,13 +832,13 @@
         <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>82.8</v>
+        <v>22.8</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>181.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>5.8</v>
@@ -851,7 +857,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>203.8</v>
+        <v>403.8</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>32.6</v>
@@ -875,7 +881,7 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>18.9</v>
@@ -887,7 +893,7 @@
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>909</v>
+        <v>99</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.2</v>
@@ -913,11 +919,11 @@
       <c r="W5" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X5" s="11" t="n">
-        <v>72.8</v>
+      <c r="X5" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>141.1</v>
+        <v>7174</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>8.199999999999999</v>
@@ -936,7 +942,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>122.3</v>
+        <v>422.3</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>34.2</v>
@@ -950,8 +956,8 @@
       <c r="G6" s="10" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="11" t="n">
-        <v>184.6</v>
+      <c r="H6" s="8" t="n">
+        <v>15.2</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>14.6</v>
@@ -974,8 +980,8 @@
       <c r="O6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="11" t="n">
-        <v>80</v>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
@@ -987,22 +993,22 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>22.8</v>
+        <v>92.8</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W6" s="11" t="n">
-        <v>31.7</v>
+        <v>28.1</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>16614.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>13.2</v>
@@ -1021,28 +1027,28 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6472.5</v>
+        <v>472.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>7.3</v>
+        <v>19.3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="G7" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G7" s="10" t="n">
         <v>15.4</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>47.9</v>
+        <v>84.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1066,7 +1072,7 @@
         <v>34.2</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
@@ -1077,7 +1083,7 @@
       <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="3" t="n">
         <v>29.5</v>
       </c>
       <c r="W7" s="3" t="n">
@@ -1090,7 +1096,7 @@
         <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1120,14 +1126,14 @@
       <c r="G8" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="8" t="n">
         <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>30.9</v>
@@ -1142,7 +1148,7 @@
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>296.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
@@ -1172,7 +1178,7 @@
         <v>26.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>20.6</v>
@@ -1191,28 +1197,28 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1781.2</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>164.8</v>
-      </c>
-      <c r="E9" s="9" t="n">
+        <v>1783.2</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="F9" s="9" t="n">
-        <v>1301.7</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>65.90000000000001</v>
+      <c r="F9" s="10" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>67.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>12.8</v>
+        <v>27.5</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>30.9</v>
@@ -1227,40 +1233,40 @@
         <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>894.2</v>
+        <v>494.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1179.6</v>
+        <v>149.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>122.9</v>
+        <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>155.1</v>
+        <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1116.8</v>
+        <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>388.8</v>
+        <v>3788.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>141.6</v>
+        <v>41.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1276,7 +1282,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8188.5</v>
+        <v>35.4</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>33</v>
@@ -1285,21 +1291,23 @@
         <v>19.4</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+        <v>5.5</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
@@ -1315,14 +1323,14 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="8" t="n">
         <v>29.9</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.8</v>
+        <v>27.1</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>66</v>
@@ -1336,14 +1344,14 @@
       <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="11" t="n">
-        <v>16.2</v>
+      <c r="X10" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>72.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>18.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1359,7 +1367,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1265.6</v>
+        <v>265.6</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>30</v>
@@ -1377,7 +1385,7 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
@@ -1392,10 +1400,10 @@
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>927.3</v>
+        <v>21.3</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
@@ -1404,31 +1412,31 @@
         <v>29.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S11" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>720.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="11" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="W11" s="11" t="n">
-        <v>16.9</v>
+      <c r="V11" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>2894</v>
+        <v>894</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>11.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1444,25 +1452,25 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>347.1</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="F12" s="3" t="n">
+        <v>242.1</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F12" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="I12" s="11" t="n">
-        <v>227.1</v>
+      <c r="I12" s="3" t="n">
+        <v>2.7</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>14.6</v>
@@ -1473,14 +1481,14 @@
       <c r="L12" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="11" t="n">
-        <v>350.5</v>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>17.9</v>
+      <c r="M12" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>927.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
@@ -1492,10 +1500,10 @@
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>21.1</v>
+        <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>51.8</v>
+        <v>59.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
@@ -1513,7 +1521,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>21.6</v>
+        <v>81.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1547,10 +1555,10 @@
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>18.3</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1576,11 +1584,11 @@
       <c r="R13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="S13" s="11" t="n">
-        <v>21.8</v>
+      <c r="S13" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>427.4</v>
+        <v>52.7</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>23.3</v>
@@ -1592,7 +1600,7 @@
         <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>77.59999999999999</v>
@@ -1632,12 +1640,14 @@
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L14" s="3" t="n">
         <v>22.4</v>
       </c>
@@ -1671,8 +1681,8 @@
       <c r="V14" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="11" t="n">
-        <v>211.6</v>
+      <c r="W14" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>25.5</v>
@@ -1680,9 +1690,7 @@
       <c r="Y14" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="Z14" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="Z14" s="3" t="inlineStr"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1697,7 +1705,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>282.8</v>
+        <v>359.6</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>32.6</v>
@@ -1715,28 +1723,28 @@
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="11" t="n">
-        <v>51.7</v>
+      <c r="K15" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>32</v>
@@ -1763,10 +1771,10 @@
         <v>28.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>738.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>100.6</v>
+        <v>10.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1782,16 +1790,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1291.2</v>
-      </c>
-      <c r="D16" s="9" t="n">
+        <v>1221.2</v>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>167.9</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>151.4</v>
+      <c r="E16" s="13" t="n">
+        <v>1255.1</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>131.9</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
@@ -1809,16 +1817,16 @@
         <v>36.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1110.6</v>
+        <v>110.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>109.5</v>
+        <v>109.8</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1230.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2490.1</v>
+        <v>1490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1827,10 +1835,10 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>121.9</v>
+        <v>1221.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.2</v>
+        <v>1136.1</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
@@ -1870,10 +1878,10 @@
         <v>318.2</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>26.4</v>
@@ -1885,13 +1893,13 @@
         <v>19.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>1.1</v>
+      <c r="K17" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
@@ -1903,13 +1911,13 @@
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>398</v>
+        <v>928</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>29.1</v>
+        <v>29.7</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>24.4</v>
@@ -1921,16 +1929,16 @@
         <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" s="11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="X17" s="11" t="n">
-        <v>84.59999999999999</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>81.5</v>
@@ -1955,7 +1963,7 @@
         <v>368</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>21.2</v>
@@ -1963,9 +1971,7 @@
       <c r="F18" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="G18" s="10" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
         <v>80.40000000000001</v>
       </c>
@@ -1973,10 +1979,10 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>6.4</v>
+        <v>14.3</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>21.4</v>
@@ -1984,11 +1990,11 @@
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="11" t="n">
-        <v>12.8</v>
+      <c r="N18" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>91.3</v>
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -1996,14 +2002,14 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
@@ -2018,10 +2024,10 @@
         <v>21.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2051,8 +2057,8 @@
       <c r="G19" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>21.4</v>
+      <c r="H19" s="8" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
@@ -2076,16 +2082,16 @@
         <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="Q19" s="11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q19" s="8" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>51.1</v>
+        <v>31.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>73.7</v>
@@ -2093,20 +2099,20 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="W19" s="11" t="n">
-        <v>289.8</v>
+      <c r="V19" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>28.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>24.1</v>
+        <v>27.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>829</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>185.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2122,31 +2128,31 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3865.9</v>
+        <v>365.9</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>31.4</v>
+        <v>38.5</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>21.5</v>
+        <v>18.5</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G20" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G20" s="10" t="n">
         <v>19.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>21.6</v>
@@ -2158,19 +2164,19 @@
         <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>928</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>20.9</v>
+        <v>30.7</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S20" s="3" t="n">
-        <v>27.5</v>
+      <c r="S20" s="8" t="n">
+        <v>17.5</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>12.3</v>
@@ -2181,17 +2187,17 @@
       <c r="V20" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="W20" s="11" t="n">
-        <v>28.8</v>
+      <c r="W20" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>21.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>125</v>
+        <v>725</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2213,7 +2219,7 @@
         <v>30.6</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="F21" s="10" t="n">
         <v>25.9</v>
@@ -2237,10 +2243,10 @@
         <v>21.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>23.6</v>
+        <v>25.6</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
@@ -2255,7 +2261,7 @@
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>91.2</v>
+        <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>71.2</v>
@@ -2266,14 +2272,14 @@
       <c r="V21" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W21" s="11" t="n">
-        <v>46.6</v>
+      <c r="W21" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>712.3</v>
+        <v>72.3</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2303,8 +2309,8 @@
       <c r="F22" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>12.8</v>
+      <c r="G22" s="10" t="n">
+        <v>11.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2316,13 +2322,13 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>24.7</v>
@@ -2337,7 +2343,7 @@
         <v>32.4</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>25.9</v>
+        <v>29.9</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>89.3</v>
@@ -2346,22 +2352,22 @@
         <v>60.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V22" s="3" t="n">
-        <v>86.5</v>
+        <v>19.2</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X22" s="11" t="n">
-        <v>29.4</v>
+      <c r="X22" s="3" t="n">
+        <v>29.7</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1244.9</v>
+        <v>144.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2377,19 +2383,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8519.6</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>1468.5</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>1074.2</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>132.4</v>
+        <v>1739.6</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>138.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>50.3</v>
+        <v>20.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>101.8</v>
@@ -2398,10 +2404,10 @@
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>104.5</v>
+        <v>10.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>495.1</v>
+        <v>49.1</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>108.2</v>
@@ -2419,7 +2425,7 @@
         <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1565.7</v>
+        <v>155.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>128.1</v>
@@ -2428,16 +2434,16 @@
         <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>3325.1</v>
+        <v>325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.4</v>
+        <v>134.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>120.3</v>
+        <v>20.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2446,7 +2452,7 @@
         <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>362.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2462,13 +2468,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.9</v>
+        <v>343.2</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>26.4</v>
@@ -2480,13 +2486,13 @@
         <v>20.4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>21.6</v>
@@ -2507,10 +2513,10 @@
         <v>31.1</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>25.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2524,14 +2530,14 @@
       <c r="W24" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X24" s="11" t="n">
-        <v>29.2</v>
+      <c r="X24" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>79.8</v>
+        <v>2981.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2558,8 +2564,8 @@
       <c r="F25" s="10" t="n">
         <v>23.5</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>8.6</v>
+      <c r="G25" s="10" t="n">
+        <v>5.7</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.2</v>
@@ -2571,7 +2577,7 @@
         <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>22.4</v>
@@ -2583,7 +2589,7 @@
         <v>26.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>914</v>
+        <v>97</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.7</v>
@@ -2592,7 +2598,7 @@
         <v>26.2</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>28.7</v>
@@ -2601,17 +2607,19 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr"/>
+        <v>5.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>14.4</v>
+      </c>
       <c r="W25" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X25" s="11" t="n">
+      <c r="X25" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>8417.4</v>
+        <v>8781.700000000001</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2630,26 +2638,26 @@
       <c r="C26" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="10" t="n">
         <v>25.1</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F26" s="3" t="n">
+      <c r="E26" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.1</v>
+        <v>14.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>6.1</v>
@@ -2661,7 +2669,7 @@
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
@@ -2673,13 +2681,13 @@
         <v>24.3</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>2.4</v>
@@ -2690,14 +2698,14 @@
       <c r="W26" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X26" s="11" t="n">
-        <v>71.09999999999999</v>
+      <c r="X26" s="3" t="n">
+        <v>27.1</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>124.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2715,14 +2723,14 @@
       <c r="C27" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D27" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" s="3" t="n">
+      <c r="D27" s="10" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E27" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>35.4</v>
+      <c r="F27" s="10" t="n">
+        <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>19.9</v>
@@ -2740,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
@@ -2757,8 +2765,8 @@
       <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="11" t="n">
-        <v>16.9</v>
+      <c r="R27" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>29</v>
@@ -2769,20 +2777,20 @@
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="3" t="n">
-        <v>86.90000000000001</v>
+      <c r="V27" s="8" t="n">
+        <v>826.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="X27" s="11" t="n">
-        <v>289</v>
+        <v>24.4</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>12.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2801,7 +2809,7 @@
         <v>290.7</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>20.5</v>
@@ -2834,10 +2842,10 @@
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>97.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
@@ -2867,7 +2875,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>107.4</v>
+        <v>10.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2885,16 +2893,16 @@
       <c r="C29" s="3" t="n">
         <v>246.8</v>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E29" s="3" t="n">
+      <c r="D29" s="10" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E29" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="G29" s="11" t="n">
+      <c r="F29" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="n">
         <v>11</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2904,7 +2912,7 @@
         <v>1.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8.4</v>
@@ -2925,7 +2933,7 @@
         <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23.6</v>
@@ -2934,10 +2942,10 @@
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>14.2</v>
+        <v>94.2</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>22.4</v>
@@ -2945,8 +2953,8 @@
       <c r="W29" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="X29" s="11" t="n">
-        <v>16.6</v>
+      <c r="X29" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>90.8</v>
@@ -2971,19 +2979,19 @@
         <v>11056.2</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1145.2</v>
+        <v>145.2</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>1103.2</v>
+        <v>103.2</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1124.2</v>
+        <v>124.2</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>196.6</v>
+        <v>296.6</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>7.1</v>
@@ -2992,7 +3000,7 @@
         <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>28.8</v>
+        <v>328.8</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>106.5</v>
@@ -3001,7 +3009,7 @@
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>125.9</v>
+        <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>487.6</v>
@@ -3013,31 +3021,29 @@
         <v>1135.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>120.1</v>
+        <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>140.9</v>
+        <v>1240.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
-      <c r="U30" s="3" t="n">
-        <v>18</v>
-      </c>
+      <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" s="3" t="n">
-        <v>1126.1</v>
+        <v>126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>115.8</v>
+        <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>132.9</v>
+        <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>28.1</v>
+        <v>85.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3055,14 +3061,14 @@
       <c r="C31" s="3" t="n">
         <v>211.2</v>
       </c>
-      <c r="D31" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>14.8</v>
+      <c r="D31" s="13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>8.4</v>
@@ -3077,7 +3083,7 @@
         <v>2.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
@@ -3089,7 +3095,7 @@
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.5</v>
+        <v>927.5</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.6</v>
@@ -3107,7 +3113,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>25.2</v>
@@ -3116,13 +3122,13 @@
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>97.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>24.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3138,25 +3144,25 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>8816.9</v>
+        <v>384.7</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>31.1</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>19.3</v>
+        <v>15.3</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G32" s="10" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H32" s="11" t="n">
+      <c r="H32" s="8" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.6</v>
@@ -3171,7 +3177,7 @@
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3185,26 +3191,26 @@
       <c r="R32" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S32" s="11" t="n">
-        <v>72.5</v>
+      <c r="S32" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>61</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>27.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>23.8</v>
+        <v>83.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>97.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>7641.6</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>19.3</v>
@@ -3250,13 +3256,13 @@
         <v>14.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>81.5</v>
+        <v>21.5</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>17.8</v>
+        <v>23.9</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3265,16 +3271,16 @@
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>22.9</v>
+        <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>20.6</v>
+        <v>28.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>20.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>11.5</v>
@@ -3282,17 +3288,17 @@
       <c r="V33" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="11" t="n">
+      <c r="W33" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>86.2</v>
+        <v>26.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.5</v>
+        <v>144.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3314,13 +3320,13 @@
         <v>31.9</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>20.2</v>
@@ -3329,7 +3335,7 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>39.5</v>
+        <v>9.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.2</v>
@@ -3350,10 +3356,10 @@
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>3</v>
+        <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.8</v>
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3374,7 +3380,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>182.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3399,7 +3405,7 @@
         <v>31.1</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>25.9</v>
@@ -3432,16 +3438,16 @@
         <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>24.9</v>
+      <c r="R35" s="8" t="n">
+        <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.8</v>
+        <v>21.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3450,19 +3456,19 @@
         <v>17.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W35" s="11" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W35" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>811.1</v>
+        <v>8.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3514,7 +3520,7 @@
         <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>98.5</v>
+        <v>97.5</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
@@ -3537,17 +3543,17 @@
       <c r="V36" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X36" s="11" t="n">
-        <v>83.90000000000001</v>
+      <c r="W36" s="8" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>11</v>
+        <v>1411</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3593,10 +3599,10 @@
         <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>105.2</v>
+        <v>103.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>126.1</v>
+        <v>124.1</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492.7</v>
@@ -3605,7 +3611,7 @@
         <v>17.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>153.1</v>
+        <v>153.7</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>126.2</v>
@@ -3614,25 +3620,25 @@
         <v>143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>8216.799999999999</v>
+        <v>324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>11.7</v>
+        <v>19.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>126.8</v>
+        <v>136.8</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>102.4</v>
+        <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>398.2</v>
+        <v>3928.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>892.1</v>
+        <v>39.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3663,7 +3669,7 @@
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2</v>
@@ -3690,20 +3696,20 @@
       <c r="Q38" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>24.3</v>
@@ -3715,7 +3721,7 @@
         <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>566.1</v>
+        <v>7.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3731,21 +3737,21 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3232.5</v>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>821.8100000000001</v>
-      </c>
-      <c r="E39" s="3" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E39" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3755,7 +3761,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>21</v>
@@ -3773,9 +3779,9 @@
         <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="R39" s="11" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="R39" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3785,13 +3791,13 @@
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V39" s="11" t="n">
-        <v>49.1</v>
+        <v>11.3</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>2.7</v>
@@ -3800,7 +3806,7 @@
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>8.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3816,7 +3822,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1534.1</v>
+        <v>153.7</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>33</v>
@@ -3834,10 +3840,10 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3867,7 +3873,7 @@
         <v>29.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>39.2</v>
+        <v>59.2</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>20.2</v>
@@ -3875,14 +3881,14 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X40" s="3" t="n">
-        <v>26.9</v>
+      <c r="X40" s="8" t="n">
+        <v>86.90000000000001</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>22.8</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>101.6</v>
@@ -3901,7 +3907,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>965.6</v>
+        <v>8985.6</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>31.6</v>
@@ -3937,7 +3943,7 @@
         <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.2</v>
@@ -3948,29 +3954,29 @@
       <c r="R41" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>24.9</v>
+      <c r="S41" s="8" t="n">
+        <v>16.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V41" s="11" t="n">
-        <v>46.6</v>
+        <v>2</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X41" s="11" t="n">
-        <v>9218</v>
+      <c r="X41" s="3" t="n">
+        <v>98</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3992,7 +3998,7 @@
         <v>31.6</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F42" s="10" t="n">
         <v>25.9</v>
@@ -4006,11 +4012,11 @@
       <c r="I42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K42" s="11" t="n">
-        <v>28.1</v>
+      <c r="J42" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>21.9</v>
@@ -4019,10 +4025,10 @@
         <v>21.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>1899</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
@@ -4042,14 +4048,14 @@
       <c r="U42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V42" s="11" t="n">
-        <v>822.9</v>
-      </c>
-      <c r="W42" s="11" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="X42" s="11" t="n">
-        <v>88.2</v>
+      <c r="V42" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>828.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>90.59999999999999</v>
@@ -4074,15 +4080,15 @@
         <v>372.2</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>29.9</v>
+        <v>28.1</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G43" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4092,7 +4098,7 @@
         <v>2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>13.7</v>
+        <v>3.7</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
@@ -4116,7 +4122,7 @@
         <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>80.40000000000001</v>
@@ -4130,17 +4136,17 @@
       <c r="V43" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W43" s="11" t="n">
-        <v>41.4</v>
+      <c r="W43" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>198.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4156,7 +4162,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>365.9</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>32.5</v>
@@ -4170,8 +4176,8 @@
       <c r="G44" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="3" t="n">
-        <v>89.40000000000001</v>
+      <c r="H44" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
@@ -4182,11 +4188,11 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="n">
-        <v>22.3</v>
+      <c r="L44" s="8" t="n">
+        <v>82.3</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>22.3</v>
+        <v>82.3</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>26.9</v>
@@ -4195,31 +4201,31 @@
         <v>100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="11" t="n">
+      <c r="R44" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>30.4</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>82.8</v>
+      <c r="X44" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>84.40000000000001</v>
@@ -4243,74 +4249,74 @@
       <c r="C45" s="3" t="n">
         <v>2026.2</v>
       </c>
-      <c r="D45" s="9" t="n">
-        <v>19165.6</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>1128</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>2026.1</v>
+      <c r="D45" s="13" t="n">
+        <v>1901.6</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>11298.6</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>226.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>9.1</v>
+        <v>2.1</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>1114.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1101</v>
+        <v>11</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>118.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>743.1</v>
+        <v>783.6</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>11665.9</v>
+        <v>1166.5</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>128.9</v>
+        <v>123.9</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>1148.8</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>292.8</v>
+        <v>293.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>172.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1469.1</v>
+        <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>174.1</v>
+        <v>121.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1450.8</v>
+        <v>1230</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>158.1</v>
       </c>
       <c r="W45" s="3" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="X45" s="3" t="n">
         <v>172.2</v>
       </c>
-      <c r="X45" s="3" t="n">
-        <v>84.5</v>
-      </c>
       <c r="Y45" s="3" t="n">
-        <v>900.1</v>
+        <v>503.4</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4329,15 +4335,15 @@
         <v>237.6</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="F46" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="G46" s="11" t="n">
+      <c r="G46" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4349,11 +4355,9 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="11" t="n">
-        <v>11.1</v>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>20</v>
@@ -4362,7 +4366,7 @@
         <v>24.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
@@ -4377,7 +4381,7 @@
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>22.9</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
@@ -4392,10 +4396,10 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>62.5</v>
+        <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +152,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -795,13 +792,13 @@
       <c r="J4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -813,7 +810,7 @@
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="10" t="n">
         <v>28.7</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -828,10 +825,10 @@
       <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -880,13 +877,13 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="10" t="n">
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -898,7 +895,7 @@
       <c r="P5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="10" t="n">
         <v>32.6</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -913,10 +910,10 @@
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="10" t="n">
         <v>24</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -965,13 +962,13 @@
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="10" t="n">
         <v>20</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -983,7 +980,7 @@
       <c r="P6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="10" t="n">
         <v>32.7</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -998,10 +995,10 @@
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="10" t="n">
         <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1050,13 +1047,13 @@
       <c r="J7" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1068,10 +1065,10 @@
       <c r="P7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="10" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="12" t="n">
         <v>2.2</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1083,10 +1080,10 @@
       <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="10" t="n">
         <v>29.5</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1135,13 +1132,13 @@
       <c r="J8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="10" t="n">
         <v>30.9</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1153,7 +1150,7 @@
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
@@ -1168,10 +1165,10 @@
       <c r="U8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1220,13 +1217,13 @@
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>30.9</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="10" t="n">
         <v>100.2</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="10" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1238,10 +1235,10 @@
       <c r="P9" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="10" t="n">
         <v>149.6</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="13" t="n">
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1253,10 +1250,10 @@
       <c r="U9" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="13" t="n">
         <v>132.8</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="10" t="n">
         <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1308,10 +1305,10 @@
       <c r="K10" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="10" t="n">
         <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1323,10 +1320,10 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="10" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="13" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1338,10 +1335,10 @@
       <c r="U10" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="10" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1393,10 +1390,10 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="10" t="n">
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1426,7 +1423,7 @@
       <c r="V11" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="12" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1478,10 +1475,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="10" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1563,10 +1560,10 @@
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1648,10 +1645,10 @@
       <c r="K14" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1663,7 +1660,7 @@
       <c r="P14" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="12" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1731,10 +1728,10 @@
       <c r="K15" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1813,13 +1810,13 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="13" t="n">
         <v>36.8</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="10" t="n">
         <v>110.6</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="13" t="n">
         <v>109.8</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1831,10 +1828,10 @@
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="13" t="n">
         <v>148.7</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="13" t="n">
         <v>1221.9</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1846,10 +1843,10 @@
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="13" t="n">
         <v>133.7</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="13" t="n">
         <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1901,10 +1898,10 @@
       <c r="K17" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1916,10 +1913,10 @@
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="13" t="n">
         <v>29.7</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="13" t="n">
         <v>24.4</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1931,10 +1928,10 @@
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="13" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="13" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1984,10 +1981,10 @@
       <c r="K18" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="10" t="n">
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1999,7 +1996,7 @@
       <c r="P18" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="10" t="n">
         <v>32.1</v>
       </c>
       <c r="R18" s="3" t="n">
@@ -2014,7 +2011,7 @@
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="10" t="n">
         <v>28.5</v>
       </c>
       <c r="W18" s="3" t="n">
@@ -2069,10 +2066,10 @@
       <c r="K19" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="10" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2084,7 +2081,7 @@
       <c r="P19" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="Q19" s="10" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
@@ -2099,7 +2096,7 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="10" t="n">
         <v>24.3</v>
       </c>
       <c r="W19" s="8" t="n">
@@ -2154,10 +2151,10 @@
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2169,7 +2166,7 @@
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="10" t="n">
         <v>30.7</v>
       </c>
       <c r="R20" s="3" t="n">
@@ -2184,7 +2181,7 @@
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="10" t="n">
         <v>27.3</v>
       </c>
       <c r="W20" s="3" t="n">
@@ -2239,10 +2236,10 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="10" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2254,7 +2251,7 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="10" t="n">
         <v>30.6</v>
       </c>
       <c r="R21" s="3" t="n">
@@ -2269,7 +2266,7 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="10" t="n">
         <v>27.8</v>
       </c>
       <c r="W21" s="8" t="n">
@@ -2324,10 +2321,10 @@
       <c r="K22" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="10" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2339,7 +2336,7 @@
       <c r="P22" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="10" t="n">
         <v>32.4</v>
       </c>
       <c r="R22" s="3" t="n">
@@ -2354,7 +2351,7 @@
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="10" t="n">
         <v>26.5</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2406,13 +2403,13 @@
       <c r="J23" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="13" t="n">
         <v>49.1</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="10" t="n">
         <v>108.2</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="13" t="n">
         <v>1107</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2424,10 +2421,10 @@
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="10" t="n">
         <v>155.7</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="13" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2439,10 +2436,10 @@
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="10" t="n">
         <v>134.4</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="13" t="n">
         <v>20.3</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2494,10 +2491,10 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2509,10 +2506,10 @@
       <c r="P24" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="13" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2524,10 +2521,10 @@
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="13" t="n">
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2582,7 +2579,7 @@
       <c r="L25" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2594,10 +2591,10 @@
       <c r="P25" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2612,7 +2609,7 @@
       <c r="V25" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2665,7 +2662,7 @@
       <c r="L26" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2677,10 +2674,10 @@
       <c r="P26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="10" t="n">
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2695,7 +2692,7 @@
       <c r="V26" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2747,10 +2744,10 @@
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="12" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="10" t="n">
         <v>20.5</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2762,10 +2759,10 @@
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2777,10 +2774,10 @@
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="8" t="n">
-        <v>826.9</v>
-      </c>
-      <c r="W27" s="3" t="n">
+      <c r="V27" s="12" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="W27" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="X27" s="8" t="n">
@@ -2835,7 +2832,7 @@
       <c r="L28" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2847,10 +2844,10 @@
       <c r="P28" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="10" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="10" t="n">
         <v>24.8</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2865,7 +2862,7 @@
       <c r="V28" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="10" t="n">
         <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2920,7 +2917,7 @@
       <c r="L29" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2932,10 +2929,10 @@
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2950,7 +2947,7 @@
       <c r="V29" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="X29" s="8" t="n">
@@ -2999,13 +2996,13 @@
       <c r="J30" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="13" t="n">
         <v>328.8</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="13" t="n">
         <v>106.5</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="10" t="n">
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3017,10 +3014,10 @@
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="13" t="n">
         <v>1135.8</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="10" t="n">
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3030,10 +3027,10 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="13" t="n">
         <v>126.1</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="10" t="n">
         <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3064,7 +3061,7 @@
       <c r="D31" s="13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="E31" s="14" t="n">
+      <c r="E31" s="12" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="F31" s="10" t="n">
@@ -3085,10 +3082,10 @@
       <c r="K31" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="13" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="10" t="n">
         <v>21</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3100,10 +3097,10 @@
       <c r="P31" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3115,10 +3112,10 @@
       <c r="U31" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="13" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3170,10 +3167,10 @@
       <c r="K32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
@@ -3185,7 +3182,7 @@
       <c r="P32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="10" t="n">
         <v>31.1</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3203,7 +3200,7 @@
       <c r="V32" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="12" t="n">
         <v>83.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3255,10 +3252,10 @@
       <c r="K33" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="10" t="n">
         <v>21.5</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3270,7 +3267,7 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="10" t="n">
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
@@ -3340,10 +3337,10 @@
       <c r="K34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="10" t="n">
         <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3355,7 +3352,7 @@
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="10" t="n">
         <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
@@ -3425,10 +3422,10 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3440,10 +3437,10 @@
       <c r="P35" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="12" t="n">
         <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3510,10 +3507,10 @@
       <c r="K36" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="10" t="n">
         <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3525,7 +3522,7 @@
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="10" t="n">
         <v>32.1</v>
       </c>
       <c r="R36" s="3" t="n">
@@ -3543,7 +3540,7 @@
       <c r="V36" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="12" t="n">
         <v>46.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3592,13 +3589,13 @@
       <c r="J37" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="13" t="n">
         <v>35.6</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="13" t="n">
         <v>1106</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="13" t="n">
         <v>103.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3610,10 +3607,10 @@
       <c r="P37" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="10" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="13" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3625,10 +3622,10 @@
       <c r="U37" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="13" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="13" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3678,10 +3675,10 @@
         <v>3.6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="10" t="n">
         <v>21</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3693,10 +3690,10 @@
       <c r="P38" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="10" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="13" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3708,10 +3705,10 @@
       <c r="U38" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="13" t="n">
         <v>27.4</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="13" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3778,10 +3775,10 @@
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="12" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="10" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3796,7 +3793,7 @@
       <c r="V39" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W39" s="3" t="n">
+      <c r="W39" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3866,7 +3863,7 @@
       <c r="Q40" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="10" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3881,7 +3878,7 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="X40" s="8" t="n">
@@ -3951,7 +3948,7 @@
       <c r="Q41" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="S41" s="8" t="n">
@@ -3966,7 +3963,7 @@
       <c r="V41" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="10" t="n">
         <v>23.4</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -4036,7 +4033,7 @@
       <c r="Q42" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4051,7 +4048,7 @@
       <c r="V42" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="10" t="n">
         <v>22.5</v>
       </c>
       <c r="X42" s="8" t="n">
@@ -4121,7 +4118,7 @@
       <c r="Q43" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="10" t="n">
         <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4136,7 +4133,7 @@
       <c r="V43" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="10" t="n">
         <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4188,10 +4185,10 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="8" t="n">
+      <c r="L44" s="12" t="n">
         <v>82.3</v>
       </c>
-      <c r="M44" s="3" t="n">
+      <c r="M44" s="12" t="n">
         <v>82.3</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4206,7 +4203,7 @@
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="10" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4221,7 +4218,7 @@
       <c r="V44" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W44" s="3" t="n">
+      <c r="W44" s="10" t="n">
         <v>26.3</v>
       </c>
       <c r="X44" s="8" t="n">
@@ -4270,13 +4267,13 @@
       <c r="J45" s="3" t="n">
         <v>118.4</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="13" t="n">
         <v>783.6</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="13" t="n">
         <v>1166.5</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="13" t="n">
         <v>123.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4288,10 +4285,10 @@
       <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="13" t="n">
         <v>172.8</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="10" t="n">
         <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4303,10 +4300,10 @@
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="13" t="n">
         <v>158.1</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="13" t="n">
         <v>128.2</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4356,10 +4353,10 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="13" t="n">
         <v>21.1</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="13" t="n">
         <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4371,10 +4368,10 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="13" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="13" t="n">
         <v>21.8</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4386,10 +4383,10 @@
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="13" t="n">
         <v>26.3</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -35,14 +35,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,8 +47,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -143,19 +137,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -769,22 +757,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E4" s="11" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="G4" s="11" t="n">
+      <c r="F4" s="8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G4" s="8" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H4" s="8" t="n">
-        <v>88.2</v>
+      <c r="H4" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>1.7</v>
@@ -792,13 +780,13 @@
       <c r="J4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" s="11" t="n">
+      <c r="K4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -810,10 +798,10 @@
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -825,13 +813,13 @@
       <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W4" s="11" t="n">
+      <c r="W4" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -854,22 +842,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>240.3</v>
-      </c>
-      <c r="D5" s="11" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="D5" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>416.8</v>
+      <c r="H5" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
@@ -877,13 +865,13 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -895,10 +883,10 @@
       <c r="P5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -910,10 +898,10 @@
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -939,18 +927,18 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>422.3</v>
-      </c>
-      <c r="D6" s="11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -962,13 +950,13 @@
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="8" t="n">
         <v>20</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -980,25 +968,25 @@
       <c r="P6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="8" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>155.8</v>
+        <v>55.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1026,38 +1014,38 @@
       <c r="C7" s="3" t="n">
         <v>472.5</v>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E7" s="11" t="n">
+      <c r="D7" s="8" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="F7" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="G7" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>64.7</v>
+        <v>4.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>2.3</v>
+        <v>23.5</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>100</v>
@@ -1065,11 +1053,11 @@
       <c r="P7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="12" t="n">
-        <v>2.5</v>
+      <c r="R7" s="8" t="n">
+        <v>25.5</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
@@ -1078,16 +1066,16 @@
         <v>50.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V7" s="12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W7" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>2.7</v>
+        <v>27.3</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>66.2</v>
@@ -1111,19 +1099,19 @@
       <c r="C8" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="8" t="n">
         <v>34.6</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
@@ -1135,10 +1123,10 @@
       <c r="K8" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1150,10 +1138,10 @@
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1165,10 +1153,10 @@
       <c r="U8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1178,7 +1166,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.6</v>
+        <v>20.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1196,16 +1184,16 @@
       <c r="C9" s="3" t="n">
         <v>178.3</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="8" t="n">
         <v>164.8</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="8" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="8" t="n">
         <v>130.8</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="8" t="n">
         <v>67.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1217,17 +1205,17 @@
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="K9" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="8" t="n">
         <v>100.2</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="8" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>118.8</v>
+        <v>15.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>494.5</v>
@@ -1235,25 +1223,25 @@
       <c r="P9" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="8" t="n">
         <v>149.6</v>
       </c>
-      <c r="R9" s="13" t="n">
+      <c r="R9" s="8" t="n">
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2329.9</v>
+        <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="V9" s="13" t="n">
+      <c r="V9" s="8" t="n">
         <v>132.8</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" s="8" t="n">
         <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1281,16 +1269,16 @@
       <c r="C10" s="3" t="n">
         <v>356.7</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="8" t="n">
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1303,10 +1291,10 @@
         <v>5.5</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="11" t="n">
+      <c r="L10" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1318,10 +1306,10 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="13" t="n">
+      <c r="R10" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1333,10 +1321,10 @@
       <c r="U10" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V10" s="13" t="n">
+      <c r="V10" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1364,34 +1352,34 @@
       <c r="C11" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="11" t="n">
+      <c r="M11" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1403,10 +1391,10 @@
       <c r="P11" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q11" s="11" t="n">
+      <c r="Q11" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R11" s="11" t="n">
+      <c r="R11" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1418,10 +1406,10 @@
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="11" t="n">
+      <c r="V11" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1431,7 +1419,7 @@
         <v>84</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>159.8</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1449,16 +1437,16 @@
       <c r="C12" s="3" t="n">
         <v>347.1</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E12" s="11" t="n">
+      <c r="D12" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1470,43 +1458,43 @@
       <c r="J12" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" s="8" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>27.5</v>
+        <v>97.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q12" s="11" t="n">
+      <c r="Q12" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="R12" s="11" t="n">
+      <c r="R12" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>58.8</v>
+        <v>57.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V12" s="11" t="n">
+      <c r="V12" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1534,16 +1522,16 @@
       <c r="C13" s="3" t="n">
         <v>428.6</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F13" s="11" t="n">
+      <c r="E13" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="H13" s="3" t="n">
@@ -1555,13 +1543,13 @@
       <c r="J13" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="K13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="M13" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1573,10 +1561,10 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="11" t="n">
+      <c r="Q13" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="11" t="n">
+      <c r="R13" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1588,11 +1576,11 @@
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="11" t="n">
+      <c r="V13" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="W13" s="12" t="n">
-        <v>2.4</v>
+      <c r="W13" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>29.3</v>
@@ -1601,7 +1589,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1619,16 +1607,16 @@
       <c r="C14" s="3" t="n">
         <v>190.3</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1640,13 +1628,13 @@
       <c r="J14" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="K14" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="M14" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1658,10 +1646,10 @@
       <c r="P14" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q14" s="11" t="n">
+      <c r="Q14" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="R14" s="11" t="n">
+      <c r="R14" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1673,10 +1661,10 @@
       <c r="U14" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V14" s="11" t="n">
+      <c r="V14" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1704,16 +1692,16 @@
       <c r="C15" s="3" t="n">
         <v>359.6</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="8" t="n">
         <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1725,17 +1713,17 @@
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K15" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="M15" s="11" t="n">
+      <c r="L15" s="8" t="n">
         <v>21.6</v>
       </c>
+      <c r="M15" s="8" t="n">
+        <v>21.6</v>
+      </c>
       <c r="N15" s="3" t="n">
-        <v>29.8</v>
+        <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>100</v>
@@ -1743,10 +1731,10 @@
       <c r="P15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1758,10 +1746,10 @@
       <c r="U15" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="V15" s="11" t="n">
+      <c r="V15" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1789,17 +1777,17 @@
       <c r="C16" s="3" t="n">
         <v>1591.2</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="8" t="n">
         <v>157.9</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="8" t="n">
         <v>105.5</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="8" t="n">
         <v>131.7</v>
       </c>
-      <c r="G16" s="12" t="n">
-        <v>35.2</v>
+      <c r="G16" s="8" t="n">
+        <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>99.2</v>
@@ -1810,32 +1798,32 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="8" t="n">
         <v>36.8</v>
       </c>
-      <c r="L16" s="13" t="n">
-        <v>1110.6</v>
-      </c>
-      <c r="M16" s="11" t="n">
+      <c r="L16" s="8" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="M16" s="8" t="n">
         <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>130.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2490.1</v>
+        <v>490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="11" t="n">
+      <c r="Q16" s="8" t="n">
         <v>148.7</v>
       </c>
-      <c r="R16" s="11" t="n">
+      <c r="R16" s="8" t="n">
         <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.1</v>
+        <v>136.1</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
@@ -1843,11 +1831,11 @@
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="11" t="n">
+      <c r="V16" s="8" t="n">
         <v>133.7</v>
       </c>
-      <c r="W16" s="13" t="n">
-        <v>2120.7</v>
+      <c r="W16" s="8" t="n">
+        <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>142.5</v>
@@ -1874,16 +1862,16 @@
       <c r="C17" s="3" t="n">
         <v>318.2</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1898,40 +1886,40 @@
       <c r="K17" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L17" s="13" t="n">
+      <c r="L17" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q17" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="R17" s="11" t="n">
+      <c r="R17" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>22.2</v>
+        <v>27.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="11" t="n">
+      <c r="V17" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="W17" s="13" t="n">
+      <c r="W17" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1959,16 +1947,16 @@
       <c r="C18" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="H18" s="3" t="n">
@@ -1986,22 +1974,22 @@
       <c r="L18" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>197.3</v>
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2013,17 +2001,17 @@
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="W18" s="11" t="n">
+      <c r="W18" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>171.7</v>
+        <v>71.7</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>11</v>
@@ -2044,16 +2032,16 @@
       <c r="C19" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2071,7 +2059,7 @@
       <c r="L19" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M19" s="8" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2083,10 +2071,10 @@
       <c r="P19" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2098,10 +2086,10 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="W19" s="11" t="n">
+      <c r="W19" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2111,7 +2099,7 @@
         <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>12.3</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2129,17 +2117,17 @@
       <c r="C20" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>29.9</v>
+      <c r="G20" s="8" t="n">
+        <v>9.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
@@ -2156,22 +2144,22 @@
       <c r="L20" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M20" s="11" t="n">
+      <c r="M20" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q20" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q20" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2183,20 +2171,20 @@
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="V20" s="12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W20" s="11" t="n">
+      <c r="V20" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W20" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2214,16 +2202,16 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="8" t="n">
         <v>9.5</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2241,7 +2229,7 @@
       <c r="L21" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="M21" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2253,10 +2241,10 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2268,17 +2256,17 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W21" s="11" t="n">
+      <c r="W21" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>72.3</v>
+        <v>77.3</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2297,19 +2285,19 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2399.3</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>1.1</v>
+      <c r="G22" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2326,26 +2314,26 @@
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M22" s="11" t="n">
+      <c r="M22" s="8" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q22" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q22" s="8" t="n">
         <v>32.4</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>89.3</v>
+        <v>29.3</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>60.5</v>
@@ -2353,10 +2341,10 @@
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="W22" s="11" t="n">
+      <c r="W22" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2366,7 +2354,7 @@
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2384,16 +2372,16 @@
       <c r="C23" s="3" t="n">
         <v>1739.6</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="8" t="n">
         <v>157.5</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="8" t="n">
         <v>107.2</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="8" t="n">
         <v>132.4</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="G23" s="8" t="n">
         <v>50.3</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2405,28 +2393,28 @@
       <c r="J23" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="K23" s="13" t="n">
+      <c r="K23" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="L23" s="13" t="n">
+      <c r="L23" s="11" t="n">
         <v>108.2</v>
       </c>
-      <c r="M23" s="13" t="n">
-        <v>10.7</v>
+      <c r="M23" s="8" t="n">
+        <v>107</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>489.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="11" t="n">
+      <c r="Q23" s="8" t="n">
         <v>155.7</v>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" s="8" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2438,11 +2426,11 @@
       <c r="U23" s="3" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="V23" s="13" t="n">
+      <c r="V23" s="8" t="n">
         <v>134.4</v>
       </c>
-      <c r="W23" s="13" t="n">
-        <v>1120.3</v>
+      <c r="W23" s="8" t="n">
+        <v>120.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2469,16 +2457,16 @@
       <c r="C24" s="3" t="n">
         <v>347.9</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2491,10 +2479,10 @@
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="13" t="n">
+      <c r="L24" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="M24" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2504,16 +2492,16 @@
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q24" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q24" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2521,20 +2509,20 @@
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="13" t="n">
+      <c r="V24" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="11" t="n">
+      <c r="W24" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>17.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2552,16 +2540,16 @@
       <c r="C25" s="3" t="n">
         <v>106.7</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="G25" s="8" t="n">
         <v>5.7</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2573,13 +2561,13 @@
       <c r="J25" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K25" s="11" t="n">
+      <c r="K25" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="L25" s="11" t="n">
+      <c r="L25" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="M25" s="10" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2591,10 +2579,10 @@
       <c r="P25" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="11" t="n">
+      <c r="R25" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2604,12 +2592,12 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="V25" s="11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2635,19 +2623,19 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>14.1</v>
+      <c r="G26" s="8" t="n">
+        <v>4.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
@@ -2658,10 +2646,10 @@
       <c r="J26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K26" s="11" t="n">
+      <c r="K26" s="8" t="n">
         <v>6.7</v>
       </c>
-      <c r="L26" s="11" t="n">
+      <c r="L26" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="M26" s="3" t="n">
@@ -2676,10 +2664,10 @@
       <c r="P26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="11" t="n">
+      <c r="R26" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2689,12 +2677,12 @@
         <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V26" s="11" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="V26" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2704,7 +2692,7 @@
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2722,16 +2710,16 @@
       <c r="C27" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D27" s="11" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E27" s="11" t="n">
+      <c r="D27" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E27" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="G27" s="8" t="n">
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2743,10 +2731,10 @@
       <c r="J27" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K27" s="11" t="n">
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" s="8" t="n">
         <v>20.7</v>
       </c>
       <c r="M27" s="3" t="n">
@@ -2756,15 +2744,15 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="11" t="n">
+      <c r="R27" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2776,10 +2764,10 @@
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="W27" s="11" t="n">
+      <c r="W27" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2789,7 +2777,7 @@
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2807,16 +2795,16 @@
       <c r="C28" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E28" s="11" t="n">
+      <c r="D28" s="8" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E28" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G28" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2828,10 +2816,10 @@
       <c r="J28" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="L28" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="M28" s="3" t="n">
@@ -2846,14 +2834,14 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2.7</v>
+        <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>60.2</v>
@@ -2861,10 +2849,10 @@
       <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2892,20 +2880,20 @@
       <c r="C29" s="3" t="n">
         <v>246.8</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F29" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="G29" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="H29" s="8" t="n">
-        <v>69.2</v>
+      <c r="H29" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.6</v>
@@ -2913,11 +2901,11 @@
       <c r="J29" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K29" s="11" t="n">
+      <c r="K29" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="L29" s="11" t="n">
-        <v>20.1</v>
+      <c r="L29" s="8" t="n">
+        <v>21.1</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>20.6</v>
@@ -2926,30 +2914,30 @@
         <v>23.9</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.5</v>
+        <v>95.3</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q29" s="12" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="R29" s="11" t="n">
+      <c r="Q29" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="R29" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="V29" s="11" t="n">
+      <c r="V29" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="W29" s="11" t="n">
+      <c r="W29" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2977,20 +2965,20 @@
       <c r="C30" s="3" t="n">
         <v>1056.2</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="8" t="n">
         <v>145.2</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="8" t="n">
         <v>103.2</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="8" t="n">
         <v>124.2</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="G30" s="8" t="n">
         <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>296.6</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>7.1</v>
@@ -2998,28 +2986,28 @@
       <c r="J30" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="K30" s="11" t="n">
+      <c r="K30" s="8" t="n">
         <v>38.8</v>
       </c>
-      <c r="L30" s="13" t="n">
+      <c r="L30" s="8" t="n">
         <v>106.5</v>
       </c>
-      <c r="M30" s="13" t="n">
+      <c r="M30" s="11" t="n">
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>2487.6</v>
+        <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q30" s="13" t="n">
-        <v>1135.8</v>
-      </c>
-      <c r="R30" s="11" t="n">
+      <c r="Q30" s="8" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="R30" s="8" t="n">
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3031,17 +3019,17 @@
       <c r="U30" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="V30" s="13" t="n">
-        <v>1126.1</v>
-      </c>
-      <c r="W30" s="11" t="n">
+      <c r="V30" s="8" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="W30" s="8" t="n">
         <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1428.7</v>
+        <v>24.7</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>25.8</v>
@@ -3062,16 +3050,16 @@
       <c r="C31" s="3" t="n">
         <v>211.2</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="G31" s="8" t="n">
         <v>8.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3084,10 +3072,10 @@
         <v>2.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="11" t="n">
+      <c r="L31" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="13" t="n">
+      <c r="M31" s="11" t="n">
         <v>21</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3099,10 +3087,10 @@
       <c r="P31" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q31" s="13" t="n">
+      <c r="Q31" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="11" t="n">
+      <c r="R31" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3112,19 +3100,19 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="V31" s="11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V31" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="11" t="n">
+      <c r="W31" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>24.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>5.2</v>
@@ -3145,19 +3133,19 @@
       <c r="C32" s="3" t="n">
         <v>384.7</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="G32" s="8" t="n">
         <v>11.8</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
@@ -3166,17 +3154,17 @@
       <c r="J32" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="K32" s="11" t="n">
+      <c r="K32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="11" t="n">
+      <c r="L32" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M32" s="11" t="n">
+      <c r="M32" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3184,7 +3172,7 @@
       <c r="P32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="11" t="n">
+      <c r="Q32" s="8" t="n">
         <v>31.1</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3199,20 +3187,20 @@
       <c r="U32" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="V32" s="11" t="n">
+      <c r="V32" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>746.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>195.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3230,50 +3218,50 @@
       <c r="C33" s="3" t="n">
         <v>213.3</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="G33" s="8" t="n">
         <v>9.6</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K33" s="11" t="n">
+      <c r="K33" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="L33" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="M33" s="11" t="n">
+      <c r="M33" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>99.7</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="11" t="n">
+      <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
@@ -3284,10 +3272,10 @@
       <c r="U33" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="V33" s="11" t="n">
+      <c r="V33" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3297,7 +3285,7 @@
         <v>0.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3315,16 +3303,16 @@
       <c r="C34" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3336,29 +3324,29 @@
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K34" s="11" t="n">
+      <c r="K34" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="11" t="n">
+      <c r="L34" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="M34" s="11" t="n">
+      <c r="M34" s="8" t="n">
         <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="11" t="n">
+      <c r="Q34" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>35.8</v>
+      <c r="R34" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3369,10 +3357,10 @@
       <c r="U34" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="V34" s="11" t="n">
+      <c r="V34" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3382,7 +3370,7 @@
         <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3398,18 +3386,18 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>353.1</v>
-      </c>
-      <c r="D35" s="11" t="n">
+        <v>353.4</v>
+      </c>
+      <c r="D35" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G35" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3421,32 +3409,32 @@
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="11" t="n">
+      <c r="K35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="L35" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="11" t="n">
+      <c r="M35" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>297.2</v>
+        <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q35" s="11" t="n">
+      <c r="Q35" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="12" t="n">
-        <v>46.9</v>
+      <c r="R35" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3454,17 +3442,17 @@
       <c r="U35" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="V35" s="11" t="n">
+      <c r="V35" s="8" t="n">
         <v>27.8</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>16.6</v>
+        <v>24.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8.4</v>
@@ -3483,18 +3471,18 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>430.7</v>
-      </c>
-      <c r="D36" s="11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D36" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="G36" s="11" t="n">
+      <c r="G36" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3506,13 +3494,13 @@
       <c r="J36" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K36" s="11" t="n">
+      <c r="K36" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="L36" s="11" t="n">
+      <c r="L36" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="11" t="n">
+      <c r="M36" s="8" t="n">
         <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3524,7 +3512,7 @@
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="11" t="n">
+      <c r="Q36" s="8" t="n">
         <v>32.1</v>
       </c>
       <c r="R36" s="3" t="n">
@@ -3539,20 +3527,20 @@
       <c r="U36" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="V36" s="11" t="n">
+      <c r="V36" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3570,16 +3558,16 @@
       <c r="C37" s="3" t="n">
         <v>1693.7</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F37" s="8" t="n">
         <v>128.7</v>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="G37" s="8" t="n">
         <v>53.4</v>
       </c>
       <c r="H37" s="3" t="n">
@@ -3591,13 +3579,13 @@
       <c r="J37" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="K37" s="11" t="n">
+      <c r="K37" s="8" t="n">
         <v>35.6</v>
       </c>
-      <c r="L37" s="13" t="n">
-        <v>1106</v>
-      </c>
-      <c r="M37" s="11" t="n">
+      <c r="L37" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="M37" s="8" t="n">
         <v>105.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3609,35 +3597,35 @@
       <c r="P37" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q37" s="11" t="n">
+      <c r="Q37" s="8" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="13" t="n">
+      <c r="R37" s="11" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1143.1</v>
+        <v>143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>2324.8</v>
+        <v>324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="V37" s="11" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="V37" s="8" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="13" t="n">
+      <c r="W37" s="8" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>392.2</v>
+        <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>139.7</v>
+        <v>39.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3655,16 +3643,16 @@
       <c r="C38" s="3" t="n">
         <v>338.7</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3677,25 +3665,25 @@
         <v>3.6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="11" t="n">
+      <c r="L38" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M38" s="11" t="n">
+      <c r="M38" s="8" t="n">
         <v>21</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="11" t="n">
+      <c r="Q38" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="13" t="n">
+      <c r="R38" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3707,17 +3695,17 @@
       <c r="U38" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V38" s="13" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="W38" s="13" t="n">
+      <c r="V38" s="8" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W38" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>29.1</v>
+        <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3738,16 +3726,16 @@
       <c r="C39" s="3" t="n">
         <v>332.5</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F39" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="8" t="n">
         <v>11.7</v>
       </c>
       <c r="H39" s="3" t="n">
@@ -3760,12 +3748,12 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L39" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L39" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="11" t="n">
+      <c r="M39" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3777,25 +3765,25 @@
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="11" t="n">
+      <c r="Q39" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="R39" s="11" t="n">
+      <c r="R39" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>163.2</v>
+        <v>63.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W39" s="11" t="n">
+      <c r="W39" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3805,7 +3793,7 @@
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>23.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3821,25 +3809,25 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1453.7</v>
-      </c>
-      <c r="D40" s="11" t="n">
+        <v>453.7</v>
+      </c>
+      <c r="D40" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.7</v>
+        <v>22.7</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5</v>
@@ -3847,10 +3835,10 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="11" t="n">
+      <c r="L40" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="11" t="n">
+      <c r="M40" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3862,10 +3850,10 @@
       <c r="P40" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q40" s="11" t="n">
+      <c r="Q40" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="11" t="n">
+      <c r="R40" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3880,7 +3868,7 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3908,16 +3896,16 @@
       <c r="C41" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="G41" s="11" t="n">
+      <c r="G41" s="8" t="n">
         <v>12</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3932,10 +3920,10 @@
       <c r="K41" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="L41" s="11" t="n">
+      <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="11" t="n">
+      <c r="M41" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3947,10 +3935,10 @@
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="11" t="n">
+      <c r="Q41" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="R41" s="11" t="n">
+      <c r="R41" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3962,17 +3950,17 @@
       <c r="U41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V41" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W41" s="11" t="n">
+      <c r="V41" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W41" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>28</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>190.5</v>
+        <v>90.5</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>2.9</v>
@@ -3993,16 +3981,16 @@
       <c r="C42" s="3" t="n">
         <v>236.3</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="G42" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4017,40 +4005,40 @@
       <c r="K42" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="L42" s="11" t="n">
+      <c r="L42" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M42" s="11" t="n">
+      <c r="M42" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="11" t="n">
+      <c r="Q42" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="11" t="n">
+      <c r="R42" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>97.2</v>
+        <v>97.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W42" s="11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="W42" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4076,16 +4064,16 @@
       <c r="C43" s="3" t="n">
         <v>372.2</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="8" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4100,10 +4088,10 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="11" t="n">
+      <c r="L43" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M43" s="11" t="n">
+      <c r="M43" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="N43" s="3" t="n">
@@ -4115,14 +4103,14 @@
       <c r="P43" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q43" s="11" t="n">
+      <c r="Q43" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R43" s="11" t="n">
+      <c r="R43" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>75.59999999999999</v>
@@ -4133,7 +4121,7 @@
       <c r="V43" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W43" s="11" t="n">
+      <c r="W43" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4161,34 +4149,34 @@
       <c r="C44" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D44" s="11" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E44" s="11" t="n">
+      <c r="D44" s="8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F44" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="G44" s="11" t="n">
+      <c r="G44" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="8" t="n">
-        <v>49.4</v>
+      <c r="H44" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="11" t="n">
+      <c r="L44" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="M44" s="11" t="n">
+      <c r="M44" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4200,10 +4188,10 @@
       <c r="P44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" s="11" t="n">
+      <c r="Q44" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="11" t="n">
+      <c r="R44" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4216,19 +4204,19 @@
         <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W44" s="11" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W44" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>184.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4246,71 +4234,71 @@
       <c r="C45" s="3" t="n">
         <v>202.6</v>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="8" t="n">
         <v>190.6</v>
       </c>
-      <c r="E45" s="13" t="n">
-        <v>1121.5</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>156.3</v>
-      </c>
-      <c r="G45" s="3" t="n">
+      <c r="E45" s="8" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="G45" s="8" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>1114.7</v>
+        <v>114.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>101.2</v>
+        <v>10.2</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K45" s="13" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="L45" s="13" t="n">
-        <v>126.3</v>
-      </c>
-      <c r="M45" s="13" t="n">
-        <v>10122.9</v>
+      <c r="K45" s="11" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>125.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1148.7</v>
+        <v>148.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>293.8</v>
+        <v>593.8</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q45" s="11" t="n">
+      <c r="Q45" s="8" t="n">
         <v>172.8</v>
       </c>
-      <c r="R45" s="11" t="n">
+      <c r="R45" s="8" t="n">
         <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>174.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>2430</v>
+        <v>250</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="13" t="n">
+      <c r="V45" s="11" t="n">
         <v>158.1</v>
       </c>
-      <c r="W45" s="11" t="n">
+      <c r="W45" s="8" t="n">
         <v>144.9</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>172.2</v>
+        <v>172.5</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>583.7</v>
+        <v>503.7</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>34</v>
@@ -4329,18 +4317,18 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>237.6</v>
-      </c>
-      <c r="D46" s="11" t="n">
+        <v>337.6</v>
+      </c>
+      <c r="D46" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="G46" s="11" t="n">
+      <c r="G46" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4353,12 +4341,12 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L46" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M46" s="11" t="n">
+      <c r="M46" s="8" t="n">
         <v>21</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4370,11 +4358,11 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="11" t="n">
+      <c r="Q46" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="13" t="n">
-        <v>21.8</v>
+      <c r="R46" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>29</v>
@@ -4385,17 +4373,17 @@
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="13" t="n">
+      <c r="V46" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>823.9</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -137,13 +137,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -927,7 +924,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.3</v>
+        <v>122.3</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>34.2</v>
@@ -1182,7 +1179,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>178.3</v>
+        <v>1783.5</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>164.8</v>
@@ -1215,7 +1212,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>15.8</v>
+        <v>115.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>494.5</v>
@@ -1251,7 +1248,7 @@
         <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.6</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1290,7 +1287,9 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L10" s="8" t="n">
         <v>20</v>
       </c>
@@ -1438,7 +1437,7 @@
         <v>347.1</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>22.6</v>
@@ -2311,8 +2310,8 @@
       <c r="K22" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>21.3</v>
+      <c r="L22" s="10" t="n">
+        <v>22.13</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>21</v>
@@ -2393,10 +2392,10 @@
       <c r="J23" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="K23" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="L23" s="9" t="n">
         <v>108.2</v>
       </c>
       <c r="M23" s="8" t="n">
@@ -2406,7 +2405,7 @@
         <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
@@ -2479,7 +2478,7 @@
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="11" t="n">
+      <c r="L24" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="M24" s="8" t="n">
@@ -2674,7 +2673,7 @@
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>92</v>
+        <v>28.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>22.9</v>
@@ -2744,7 +2743,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2811,7 +2810,7 @@
         <v>18.9</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -2832,7 +2831,7 @@
         <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q28" s="8" t="n">
         <v>31.2</v>
@@ -2992,7 +2991,7 @@
       <c r="L30" s="8" t="n">
         <v>106.5</v>
       </c>
-      <c r="M30" s="11" t="n">
+      <c r="M30" s="9" t="n">
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3007,8 +3006,8 @@
       <c r="Q30" s="8" t="n">
         <v>135.8</v>
       </c>
-      <c r="R30" s="8" t="n">
-        <v>120.7</v>
+      <c r="R30" s="9" t="n">
+        <v>1207.2</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>140.9</v>
@@ -3017,7 +3016,7 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>126.1</v>
@@ -3029,7 +3028,7 @@
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>24.7</v>
+        <v>424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>25.8</v>
@@ -3069,13 +3068,13 @@
         <v>1.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="11" t="n">
+      <c r="M31" s="9" t="n">
         <v>21</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3100,7 +3099,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>25.2</v>
@@ -3175,7 +3174,7 @@
       <c r="Q32" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3190,7 +3189,7 @@
       <c r="V32" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3252,7 +3251,7 @@
         <v>25.4</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99.7</v>
+        <v>99</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
@@ -3260,8 +3259,8 @@
       <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>22.6</v>
+      <c r="R33" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
@@ -3275,7 +3274,7 @@
       <c r="V33" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3345,7 +3344,7 @@
       <c r="Q34" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3360,7 +3359,7 @@
       <c r="V34" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W34" s="8" t="n">
+      <c r="W34" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3430,7 +3429,7 @@
       <c r="Q35" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3445,14 +3444,14 @@
       <c r="V35" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W35" s="8" t="n">
-        <v>24.6</v>
+      <c r="W35" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8.4</v>
@@ -3471,7 +3470,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>30.7</v>
+        <v>430.7</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>32.1</v>
@@ -3515,7 +3514,7 @@
       <c r="Q36" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3530,7 +3529,7 @@
       <c r="V36" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3600,7 +3599,7 @@
       <c r="Q37" s="8" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="11" t="n">
+      <c r="R37" s="8" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3615,14 +3614,14 @@
       <c r="V37" s="8" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="8" t="n">
+      <c r="W37" s="9" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>122.4</v>
+        <v>142.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>398.2</v>
+        <v>392.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>39.7</v>
@@ -3683,7 +3682,7 @@
       <c r="Q38" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3698,14 +3697,14 @@
       <c r="V38" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W38" s="8" t="n">
+      <c r="W38" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3730,7 +3729,7 @@
         <v>31.9</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>26.1</v>
@@ -3748,7 +3747,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>21</v>
@@ -3780,7 +3779,7 @@
       <c r="U39" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="W39" s="8" t="n">
@@ -3827,7 +3826,7 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>22.7</v>
+        <v>2.7</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5</v>
@@ -3865,7 +3864,7 @@
       <c r="U40" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="8" t="n">
         <v>27.8</v>
       </c>
       <c r="W40" s="8" t="n">
@@ -3950,7 +3949,7 @@
       <c r="U41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="W41" s="8" t="n">
@@ -4000,7 +3999,7 @@
         <v>0.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>28.7</v>
@@ -4035,8 +4034,8 @@
       <c r="U42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>22.7</v>
+      <c r="V42" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="W42" s="8" t="n">
         <v>23.5</v>
@@ -4118,7 +4117,7 @@
       <c r="U43" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="8" t="n">
         <v>27.8</v>
       </c>
       <c r="W43" s="8" t="n">
@@ -4203,7 +4202,7 @@
       <c r="U44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="8" t="n">
         <v>28.5</v>
       </c>
       <c r="W44" s="8" t="n">
@@ -4232,18 +4231,18 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>202.6</v>
+        <v>2026.2</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>190.6</v>
       </c>
-      <c r="E45" s="8" t="n">
-        <v>121.5</v>
-      </c>
-      <c r="F45" s="8" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="G45" s="8" t="n">
+      <c r="E45" s="9" t="n">
+        <v>1215.2</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>156.3</v>
+      </c>
+      <c r="G45" s="3" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
@@ -4255,8 +4254,8 @@
       <c r="J45" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K45" s="11" t="n">
-        <v>72.3</v>
+      <c r="K45" s="9" t="n">
+        <v>78.3</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>126.5</v>
@@ -4283,12 +4282,12 @@
         <v>174.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="11" t="n">
+      <c r="V45" s="8" t="n">
         <v>158.1</v>
       </c>
       <c r="W45" s="8" t="n">
@@ -4358,8 +4357,8 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="8" t="n">
-        <v>28.8</v>
+      <c r="Q46" s="9" t="n">
+        <v>228.8</v>
       </c>
       <c r="R46" s="8" t="n">
         <v>24.8</v>
@@ -4373,7 +4372,7 @@
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="11" t="n">
+      <c r="V46" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="W46" s="8" t="n">
@@ -4383,7 +4382,7 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>122.3</v>
+        <v>422.3</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>34.2</v>
@@ -1163,7 +1163,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.5</v>
+        <v>178.3</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>164.8</v>
@@ -1248,7 +1248,7 @@
         <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>22.8</v>
+        <v>41.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1287,9 +1287,7 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="8" t="n">
         <v>20</v>
       </c>
@@ -1883,7 +1881,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>22.1</v>
@@ -2295,8 +2293,8 @@
       <c r="F22" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="G22" s="8" t="n">
-        <v>11.8</v>
+      <c r="G22" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2310,8 +2308,8 @@
       <c r="K22" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="L22" s="10" t="n">
-        <v>22.13</v>
+      <c r="L22" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>21</v>
@@ -2673,10 +2671,10 @@
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>28.2</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>22.9</v>
+        <v>2</v>
       </c>
       <c r="V26" s="8" t="n">
         <v>23.8</v>
@@ -2743,7 +2741,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2810,7 +2808,7 @@
         <v>18.9</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -3006,8 +3004,8 @@
       <c r="Q30" s="8" t="n">
         <v>135.8</v>
       </c>
-      <c r="R30" s="9" t="n">
-        <v>1207.2</v>
+      <c r="R30" s="8" t="n">
+        <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>140.9</v>
@@ -3016,7 +3014,7 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>126.1</v>
@@ -3047,7 +3045,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>211.2</v>
+        <v>21.1</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>29</v>
@@ -3068,7 +3066,7 @@
         <v>1.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="8" t="n">
@@ -3099,7 +3097,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>25.2</v>
@@ -3189,7 +3187,7 @@
       <c r="V32" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3274,7 +3272,7 @@
       <c r="V33" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3359,7 +3357,7 @@
       <c r="V34" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3444,8 +3442,8 @@
       <c r="V35" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W35" s="3" t="n">
-        <v>26.6</v>
+      <c r="W35" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
@@ -3529,7 +3527,7 @@
       <c r="V36" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3573,7 +3571,7 @@
         <v>96.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>110.1</v>
+        <v>10.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>18.1</v>
@@ -3614,14 +3612,14 @@
       <c r="V37" s="8" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="8" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>142.4</v>
+        <v>182.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>392.2</v>
+        <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>39.7</v>
@@ -3697,7 +3695,7 @@
       <c r="V38" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3729,7 +3727,7 @@
         <v>31.9</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>26.1</v>
@@ -3874,7 +3872,7 @@
         <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>10.4</v>
@@ -4231,18 +4229,18 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2026.2</v>
+        <v>202.6</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>190.6</v>
       </c>
-      <c r="E45" s="9" t="n">
-        <v>1215.2</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>156.3</v>
-      </c>
-      <c r="G45" s="3" t="n">
+      <c r="E45" s="8" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="G45" s="8" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
@@ -4340,7 +4338,7 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>21.1</v>
@@ -4357,8 +4355,8 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="9" t="n">
-        <v>228.8</v>
+      <c r="Q46" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="R46" s="8" t="n">
         <v>24.8</v>
@@ -4382,7 +4380,7 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -153,6 +165,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -795,7 +813,7 @@
       <c r="J4" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
@@ -880,7 +898,7 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
@@ -965,7 +983,7 @@
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
@@ -1050,7 +1068,7 @@
       <c r="J7" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
@@ -1135,7 +1153,7 @@
       <c r="J8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="10" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
@@ -1220,7 +1238,7 @@
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>30.9</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1811,7 +1829,7 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="13" t="n"/>
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n">
         <v>109.5</v>
@@ -1975,7 +1993,7 @@
       <c r="J18" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="K18" s="3" t="n"/>
+      <c r="K18" s="14" t="n"/>
       <c r="L18" s="3" t="n">
         <v>22.1</v>
       </c>
@@ -2377,10 +2395,10 @@
       <c r="C23" s="3" t="n">
         <v>1739.6</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="16" t="n">
         <v>2.2</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="16" t="n">
         <v>3.7</v>
       </c>
       <c r="F23" s="10" t="n">
@@ -2398,7 +2416,7 @@
       <c r="J23" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="16" t="n">
         <v>7.7</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2993,7 +3011,7 @@
       <c r="J30" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="16" t="n">
         <v>38.8</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3588,7 +3606,7 @@
       <c r="J37" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="16" t="n">
         <v>35.6</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4268,7 +4286,7 @@
       <c r="J45" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
